--- a/IA_CCBS_BANK_SIDE/AccountOther/LoanAccountOpening_InstantProcess.xlsx
+++ b/IA_CCBS_BANK_SIDE/AccountOther/LoanAccountOpening_InstantProcess.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20401"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sw\Relational_Files\Interfaces_aa\Interfaces\IA_CCBS_BANK_SIDE\AccountOther\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sw\Relational_Files\iApply\Interfaces\Interfaces_plus_allbanks\IA_CCBS_BANK_SIDE\AccountOther\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAB67502-D788-422B-A7B5-FE1FFC3D3460}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E31733D-87A5-434A-9D65-671FA85B02E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12570" xr2:uid="{68F28061-2ECD-4B0A-AB1D-3A449686159F}"/>
+    <workbookView xWindow="28680" yWindow="-5550" windowWidth="30960" windowHeight="16920" xr2:uid="{68F28061-2ECD-4B0A-AB1D-3A449686159F}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="3" r:id="rId1"/>
@@ -18,8 +18,8 @@
     <sheet name="Response" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Request!$C$2:$F$65</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Response!$C$2:$F$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Request!$D$3:$G$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Response!$D$3:$G$15</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="107">
   <si>
     <t>Description</t>
   </si>
@@ -336,7 +336,22 @@
     <t>profitsaccountcd</t>
   </si>
   <si>
-    <t>Sept 6 2023</t>
+    <t>Sept 6 2023,June 3 2025</t>
+  </si>
+  <si>
+    <t>Loan Account IBAN</t>
+  </si>
+  <si>
+    <t>iban_account</t>
+  </si>
+  <si>
+    <t>varchar(120)</t>
+  </si>
+  <si>
+    <t>Loan Account IBAN Check Digit</t>
+  </si>
+  <si>
+    <t>iban_account_cd</t>
   </si>
 </sst>
 </file>
@@ -456,7 +471,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -475,14 +490,8 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="7">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -505,76 +514,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -633,30 +579,25 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -664,288 +605,36 @@
     <cellStyle name="60% - Accent4" xfId="2" builtinId="44"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="24">
+  <dxfs count="22">
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
+        <color rgb="FF9C0006"/>
       </font>
       <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
+        <color rgb="FF9C0006"/>
       </font>
       <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
+        <color rgb="FF9C0006"/>
       </font>
       <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <charset val="161"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -997,25 +686,156 @@
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
+          <bgColor auto="1"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="161"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
         <right style="thin">
           <color indexed="64"/>
         </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -1038,26 +858,10 @@
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
+          <bgColor auto="1"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1079,26 +883,10 @@
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
+          <bgColor auto="1"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1120,26 +908,10 @@
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
+          <bgColor auto="1"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1161,76 +933,53 @@
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
+          <bgColor auto="1"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1247,9 +996,9 @@
         <scheme val="minor"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill patternType="none">
           <fgColor indexed="64"/>
-          <bgColor theme="9" tint="0.79998168889431442"/>
+          <bgColor auto="1"/>
         </patternFill>
       </fill>
       <border diagonalUp="0" diagonalDown="0" outline="0">
@@ -1262,16 +1011,6 @@
         <top/>
         <bottom/>
       </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1287,41 +1026,41 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A6ACF92C-1104-4C93-8F8B-A938A4312D3B}" name="Table2" displayName="Table2" ref="A1:F30" totalsRowShown="0" headerRowDxfId="22" headerRowBorderDxfId="21" tableBorderDxfId="20" totalsRowBorderDxfId="19" headerRowCellStyle="Normal" dataCellStyle="Normal">
-  <sortState ref="A2:F30">
-    <sortCondition ref="A2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A6ACF92C-1104-4C93-8F8B-A938A4312D3B}" name="Table2" displayName="Table2" ref="B2:G31" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20" headerRowCellStyle="Normal" dataCellStyle="Normal">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:G31">
+    <sortCondition ref="B3"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{85C05364-CF34-480B-84A9-1E752A61B8E7}" name="Seq" dataDxfId="18" dataCellStyle="Normal"/>
-    <tableColumn id="2" xr3:uid="{B74F6632-9589-464E-84C1-0830E8F1F8D8}" name="Description" dataDxfId="17" dataCellStyle="Normal"/>
-    <tableColumn id="3" xr3:uid="{9572A906-3602-4DBD-9459-262F500E1D9A}" name="iApply" dataDxfId="16" dataCellStyle="Normal"/>
-    <tableColumn id="4" xr3:uid="{88CBB51C-2237-4EBC-90F4-9EFEDD4BEC32}" name="Data Type" dataDxfId="15" dataCellStyle="Normal"/>
-    <tableColumn id="6" xr3:uid="{543BB0EE-DFCA-4B94-847F-73C897029E52}" name="Entities" dataDxfId="14"/>
-    <tableColumn id="5" xr3:uid="{2E373EFE-D19B-41E5-92FD-B165DCC3E8F5}" name="Notes" dataDxfId="13" dataCellStyle="Normal"/>
+    <tableColumn id="1" xr3:uid="{85C05364-CF34-480B-84A9-1E752A61B8E7}" name="Seq" dataDxfId="19" dataCellStyle="Normal"/>
+    <tableColumn id="2" xr3:uid="{B74F6632-9589-464E-84C1-0830E8F1F8D8}" name="Description" dataDxfId="18" dataCellStyle="Normal"/>
+    <tableColumn id="3" xr3:uid="{9572A906-3602-4DBD-9459-262F500E1D9A}" name="iApply" dataDxfId="17" dataCellStyle="Normal"/>
+    <tableColumn id="4" xr3:uid="{88CBB51C-2237-4EBC-90F4-9EFEDD4BEC32}" name="Data Type" dataDxfId="16" dataCellStyle="Normal"/>
+    <tableColumn id="6" xr3:uid="{543BB0EE-DFCA-4B94-847F-73C897029E52}" name="Entities" dataDxfId="15"/>
+    <tableColumn id="5" xr3:uid="{2E373EFE-D19B-41E5-92FD-B165DCC3E8F5}" name="Notes" dataDxfId="14" dataCellStyle="Normal"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F11F741B-5D22-4BBF-9B93-935C1585CBED}" name="Table22" displayName="Table22" ref="A1:F9" totalsRowShown="0" headerRowDxfId="9" headerRowBorderDxfId="8" tableBorderDxfId="7" totalsRowBorderDxfId="6" headerRowCellStyle="Normal" dataCellStyle="Normal">
-  <autoFilter ref="A1:F9" xr:uid="{FE54AB27-2F61-427B-9D73-DA77A59601D2}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F11F741B-5D22-4BBF-9B93-935C1585CBED}" name="Table22" displayName="Table22" ref="B2:G12" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12" headerRowCellStyle="Normal" dataCellStyle="Normal">
+  <autoFilter ref="B2:G12" xr:uid="{FE54AB27-2F61-427B-9D73-DA77A59601D2}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{F8F1211F-EA34-4B44-896A-D528AAFAE184}" name="Seq" dataDxfId="5" dataCellStyle="Normal"/>
-    <tableColumn id="2" xr3:uid="{03B9C3AE-C4F7-4512-A115-C772590AED2F}" name="Description" dataDxfId="4" dataCellStyle="Normal"/>
-    <tableColumn id="3" xr3:uid="{86EE5336-821C-4C56-8460-1456EB6E1740}" name="iApply" dataDxfId="3" dataCellStyle="Normal"/>
-    <tableColumn id="7" xr3:uid="{33764DB6-8011-4E1D-A09A-295251C6CCE7}" name="Data Type" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{AC1C2596-97D1-445C-B651-3EAD2A6C7064}" name="Entities" dataDxfId="1" dataCellStyle="Normal"/>
-    <tableColumn id="5" xr3:uid="{8FD2DAF4-1939-4C6D-BEB9-074AFC032812}" name="Notes" dataDxfId="0" dataCellStyle="Normal"/>
+    <tableColumn id="1" xr3:uid="{F8F1211F-EA34-4B44-896A-D528AAFAE184}" name="Seq" dataDxfId="11" dataCellStyle="Normal"/>
+    <tableColumn id="2" xr3:uid="{03B9C3AE-C4F7-4512-A115-C772590AED2F}" name="Description" dataDxfId="10" dataCellStyle="Normal"/>
+    <tableColumn id="3" xr3:uid="{86EE5336-821C-4C56-8460-1456EB6E1740}" name="iApply" dataDxfId="9" dataCellStyle="Normal"/>
+    <tableColumn id="7" xr3:uid="{33764DB6-8011-4E1D-A09A-295251C6CCE7}" name="Data Type" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{AC1C2596-97D1-445C-B651-3EAD2A6C7064}" name="Entities" dataDxfId="7" dataCellStyle="Normal"/>
+    <tableColumn id="5" xr3:uid="{8FD2DAF4-1939-4C6D-BEB9-074AFC032812}" name="Notes" dataDxfId="6" dataCellStyle="Normal"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1359,7 +1098,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1465,7 +1204,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1607,7 +1346,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1654,10 +1393,10 @@
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="25" t="s">
+      <c r="B6" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="24" t="s">
+      <c r="C6" s="20" t="s">
         <v>101</v>
       </c>
     </row>
@@ -1701,7 +1440,7 @@
       <c r="B13" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="24" t="s">
+      <c r="C13" s="20" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1716,1073 +1455,1075 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03AC1DB5-1548-45C4-B0E5-7097191C5328}">
-  <dimension ref="A1:F104"/>
+  <dimension ref="B1:G105"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.85546875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="17.85546875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="67.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="1.42578125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="6.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.85546875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.85546875" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
+    <row r="1" spans="2:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="22" t="s">
+      <c r="C2" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="22" t="s">
+      <c r="D2" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="E2" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="23" t="s">
+      <c r="F2" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="23" t="s">
+      <c r="G2" s="22" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="20">
+    <row r="3" spans="2:7" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3">
         <v>1</v>
       </c>
-      <c r="B2" s="26" t="s">
+      <c r="C3" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="26" t="s">
+      <c r="D3" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="D2" s="26" t="s">
+      <c r="E3" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="26" t="s">
+      <c r="F3" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="27"/>
-    </row>
-    <row r="3" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="20">
+      <c r="G3" s="26"/>
+    </row>
+    <row r="4" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4">
         <v>2</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="C4" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="D4" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="26" t="s">
+      <c r="E4" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="E3" s="26" t="s">
+      <c r="F4" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="F3" s="27"/>
-    </row>
-    <row r="4" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="20">
+      <c r="G4" s="26"/>
+    </row>
+    <row r="5" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5">
         <v>3</v>
       </c>
-      <c r="B4" s="26" t="s">
+      <c r="C5" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="D5" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="E5" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="F5" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="27"/>
-    </row>
-    <row r="5" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="20">
+      <c r="G5" s="26"/>
+    </row>
+    <row r="6" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6">
         <v>4</v>
       </c>
-      <c r="B5" s="26" t="s">
+      <c r="C6" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="26" t="s">
+      <c r="D6" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="D5" s="26" t="s">
+      <c r="E6" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="26" t="s">
+      <c r="F6" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="27"/>
-    </row>
-    <row r="6" spans="1:6" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="20">
+      <c r="G6" s="26"/>
+    </row>
+    <row r="7" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7">
         <v>5</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="C7" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="D7" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="D6" s="26" t="s">
+      <c r="E7" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="26" t="s">
+      <c r="F7" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="27"/>
-    </row>
-    <row r="7" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="20">
+      <c r="G7" s="26"/>
+    </row>
+    <row r="8" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8">
         <v>6</v>
       </c>
-      <c r="B7" s="26" t="s">
+      <c r="C8" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="D8" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="D7" s="26" t="s">
+      <c r="E8" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="E7" s="26" t="s">
+      <c r="F8" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="F7" s="28"/>
-    </row>
-    <row r="8" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="20">
+      <c r="G8" s="27"/>
+    </row>
+    <row r="9" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9">
         <v>7</v>
       </c>
-      <c r="B8" s="26" t="s">
+      <c r="C9" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="D9" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="D8" s="26" t="s">
+      <c r="E9" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="26" t="s">
+      <c r="F9" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="F8" s="27"/>
-    </row>
-    <row r="9" spans="1:6" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="20">
+      <c r="G9" s="26"/>
+    </row>
+    <row r="10" spans="2:7" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10">
         <v>8</v>
       </c>
-      <c r="B9" s="26" t="s">
+      <c r="C10" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="26" t="s">
+      <c r="D10" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="26" t="s">
+      <c r="E10" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="26" t="s">
+      <c r="F10" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="F9" s="28"/>
-    </row>
-    <row r="10" spans="1:6" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="20">
+      <c r="G10" s="27"/>
+    </row>
+    <row r="11" spans="2:7" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11">
         <v>9</v>
       </c>
-      <c r="B10" s="26" t="s">
+      <c r="C11" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="26" t="s">
+      <c r="D11" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="26" t="s">
+      <c r="E11" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="E10" s="26" t="s">
+      <c r="F11" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="F10" s="27"/>
-    </row>
-    <row r="11" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="20">
+      <c r="G11" s="26"/>
+    </row>
+    <row r="12" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12">
         <v>10</v>
       </c>
-      <c r="B11" s="26" t="s">
+      <c r="C12" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="26" t="s">
+      <c r="D12" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="26" t="s">
+      <c r="E12" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="E11" s="26" t="s">
+      <c r="F12" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="F11" s="27"/>
-    </row>
-    <row r="12" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="20">
+      <c r="G12" s="26"/>
+    </row>
+    <row r="13" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13">
         <v>11</v>
       </c>
-      <c r="B12" s="29" t="s">
+      <c r="C13" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="26" t="s">
+      <c r="D13" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="D12" s="26" t="s">
+      <c r="E13" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="26" t="s">
+      <c r="F13" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="F12" s="27"/>
-    </row>
-    <row r="13" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="20">
+      <c r="G13" s="26"/>
+    </row>
+    <row r="14" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14">
         <v>12</v>
       </c>
-      <c r="B13" s="26" t="s">
+      <c r="C14" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="C13" s="26" t="s">
+      <c r="D14" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="D13" s="26" t="s">
+      <c r="E14" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="E13" s="26" t="s">
+      <c r="F14" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="F13" s="27"/>
-    </row>
-    <row r="14" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="20">
+      <c r="G14" s="26"/>
+    </row>
+    <row r="15" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15">
         <v>13</v>
       </c>
-      <c r="B14" s="26" t="s">
+      <c r="C15" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="C14" s="26" t="s">
+      <c r="D15" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="D14" s="26" t="s">
+      <c r="E15" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="E14" s="26" t="s">
+      <c r="F15" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="F14" s="27"/>
-    </row>
-    <row r="15" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="20">
+      <c r="G15" s="26"/>
+    </row>
+    <row r="16" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16">
         <v>14</v>
       </c>
-      <c r="B15" s="26" t="s">
+      <c r="C16" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="C15" s="26" t="s">
+      <c r="D16" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="D15" s="26" t="s">
+      <c r="E16" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="E15" s="26" t="s">
+      <c r="F16" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="F15" s="27"/>
-    </row>
-    <row r="16" spans="1:6" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="20">
+      <c r="G16" s="26"/>
+    </row>
+    <row r="17" spans="2:7" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17">
         <v>15</v>
       </c>
-      <c r="B16" s="26" t="s">
+      <c r="C17" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="C16" s="26" t="s">
+      <c r="D17" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="D16" s="26" t="s">
+      <c r="E17" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="E16" s="26" t="s">
+      <c r="F17" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="F16" s="27"/>
-    </row>
-    <row r="17" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="20">
+      <c r="G17" s="26"/>
+    </row>
+    <row r="18" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18">
         <v>16</v>
       </c>
-      <c r="B17" s="26" t="s">
+      <c r="C18" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="C17" s="26" t="s">
+      <c r="D18" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="D17" s="26" t="s">
+      <c r="E18" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="E17" s="26" t="s">
+      <c r="F18" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="F17" s="27"/>
-    </row>
-    <row r="18" spans="1:6" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="20">
+      <c r="G18" s="26"/>
+    </row>
+    <row r="19" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19">
         <v>17</v>
       </c>
-      <c r="B18" s="26" t="s">
+      <c r="C19" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="C18" s="26" t="s">
+      <c r="D19" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="D18" s="26" t="s">
+      <c r="E19" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="E18" s="26" t="s">
+      <c r="F19" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="F18" s="27"/>
-    </row>
-    <row r="19" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="20">
+      <c r="G19" s="26"/>
+    </row>
+    <row r="20" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20">
         <v>18</v>
       </c>
-      <c r="B19" s="26" t="s">
+      <c r="C20" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="C19" s="26" t="s">
+      <c r="D20" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="D19" s="26" t="s">
+      <c r="E20" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="E19" s="26" t="s">
+      <c r="F20" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="F19" s="27"/>
-    </row>
-    <row r="20" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="20">
+      <c r="G20" s="26"/>
+    </row>
+    <row r="21" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21">
         <v>19</v>
       </c>
-      <c r="B20" s="26" t="s">
+      <c r="C21" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="C20" s="26" t="s">
+      <c r="D21" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="D20" s="26" t="s">
+      <c r="E21" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="E20" s="26" t="s">
+      <c r="F21" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="F20" s="27"/>
-    </row>
-    <row r="21" spans="1:6" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="20">
+      <c r="G21" s="26"/>
+    </row>
+    <row r="22" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22">
         <v>20</v>
       </c>
-      <c r="B21" s="26" t="s">
+      <c r="C22" s="26" t="s">
         <v>66</v>
       </c>
-      <c r="C21" s="26" t="s">
+      <c r="D22" s="26" t="s">
         <v>67</v>
       </c>
-      <c r="D21" s="26" t="s">
+      <c r="E22" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="E21" s="26" t="s">
+      <c r="F22" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="F21" s="27"/>
-    </row>
-    <row r="22" spans="1:6" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="20">
+      <c r="G22" s="26"/>
+    </row>
+    <row r="23" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23">
         <v>21</v>
       </c>
-      <c r="B22" s="26" t="s">
+      <c r="C23" s="26" t="s">
         <v>68</v>
       </c>
-      <c r="C22" s="26" t="s">
+      <c r="D23" s="26" t="s">
         <v>69</v>
       </c>
-      <c r="D22" s="26" t="s">
+      <c r="E23" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="E22" s="26" t="s">
+      <c r="F23" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="F22" s="27"/>
-    </row>
-    <row r="23" spans="1:6" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="20">
+      <c r="G23" s="26"/>
+    </row>
+    <row r="24" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24">
         <v>22</v>
       </c>
-      <c r="B23" s="26" t="s">
+      <c r="C24" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="C23" s="26" t="s">
+      <c r="D24" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="D23" s="26" t="s">
+      <c r="E24" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="E23" s="26" t="s">
+      <c r="F24" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="F23" s="27"/>
-    </row>
-    <row r="24" spans="1:6" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="20">
+      <c r="G24" s="26"/>
+    </row>
+    <row r="25" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25">
         <v>23</v>
       </c>
-      <c r="B24" s="26" t="s">
+      <c r="C25" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="C24" s="26" t="s">
+      <c r="D25" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="D24" s="26" t="s">
+      <c r="E25" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="E24" s="26" t="s">
+      <c r="F25" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="F24" s="27"/>
-    </row>
-    <row r="25" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="20">
+      <c r="G25" s="26"/>
+    </row>
+    <row r="26" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26">
         <v>24</v>
       </c>
-      <c r="B25" s="26" t="s">
+      <c r="C26" s="26" t="s">
         <v>73</v>
       </c>
-      <c r="C25" s="26" t="s">
+      <c r="D26" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="D25" s="26" t="s">
+      <c r="E26" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="E25" s="26" t="s">
+      <c r="F26" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="F25" s="27"/>
-    </row>
-    <row r="26" spans="1:6" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="20">
+      <c r="G26" s="26"/>
+    </row>
+    <row r="27" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27">
         <v>25</v>
       </c>
-      <c r="B26" s="26"/>
-      <c r="C26" s="26" t="s">
+      <c r="C27" s="26"/>
+      <c r="D27" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="D26" s="26" t="s">
+      <c r="E27" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="E26" s="26" t="s">
+      <c r="F27" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="F26" s="27">
+      <c r="G27" s="26">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="20">
+    <row r="28" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28">
         <v>26</v>
       </c>
-      <c r="B27" s="26" t="s">
+      <c r="C28" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="C27" s="26" t="s">
+      <c r="D28" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="D27" s="26" t="s">
+      <c r="E28" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="E27" s="26" t="s">
+      <c r="F28" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="F27" s="28"/>
-    </row>
-    <row r="28" spans="1:6" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="20">
+      <c r="G28" s="27"/>
+    </row>
+    <row r="29" spans="2:7" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29">
         <v>27</v>
       </c>
-      <c r="B28" s="26" t="s">
+      <c r="C29" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="C28" s="26" t="s">
+      <c r="D29" s="26" t="s">
         <v>78</v>
       </c>
-      <c r="D28" s="26" t="s">
+      <c r="E29" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="E28" s="26" t="s">
+      <c r="F29" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="F28" s="27"/>
-    </row>
-    <row r="29" spans="1:6" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="20">
+      <c r="G29" s="26"/>
+    </row>
+    <row r="30" spans="2:7" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30">
         <v>28</v>
       </c>
-      <c r="B29" s="26" t="s">
+      <c r="C30" s="26" t="s">
         <v>79</v>
       </c>
-      <c r="C29" s="26" t="s">
+      <c r="D30" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="D29" s="26" t="s">
+      <c r="E30" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="E29" s="26" t="s">
+      <c r="F30" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="F29" s="27"/>
-    </row>
-    <row r="30" spans="1:6" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="20">
+      <c r="G30" s="26"/>
+    </row>
+    <row r="31" spans="2:7" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31">
         <v>29</v>
       </c>
-      <c r="B30" s="26" t="s">
+      <c r="C31" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="C30" s="26" t="s">
+      <c r="D31" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="D30" s="26" t="s">
+      <c r="E31" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="E30" s="26" t="s">
+      <c r="F31" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="F30" s="27"/>
-    </row>
-    <row r="31" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="3"/>
-      <c r="B31" s="3"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="6"/>
-    </row>
-    <row r="32" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C32" s="5"/>
+      <c r="G31" s="26"/>
+    </row>
+    <row r="32" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
       <c r="D32" s="5"/>
       <c r="E32" s="5"/>
-      <c r="F32" s="6"/>
-    </row>
-    <row r="33" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="1"/>
-      <c r="B33" s="1"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="8"/>
-    </row>
-    <row r="34" spans="1:6" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2"/>
-      <c r="C34" s="5"/>
-      <c r="D34" s="5"/>
-      <c r="E34" s="5"/>
-      <c r="F34" s="6"/>
-    </row>
-    <row r="35" spans="1:6" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="2"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="6"/>
+    </row>
+    <row r="33" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="6"/>
+    </row>
+    <row r="34" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="8"/>
+    </row>
+    <row r="35" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="2"/>
-      <c r="C35" s="5"/>
+      <c r="C35" s="2"/>
       <c r="D35" s="5"/>
       <c r="E35" s="5"/>
-      <c r="F35" s="6"/>
-    </row>
-    <row r="36" spans="1:6" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C36" s="5"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="6"/>
+    </row>
+    <row r="36" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
       <c r="D36" s="5"/>
       <c r="E36" s="5"/>
-      <c r="F36" s="6"/>
-    </row>
-    <row r="37" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C37" s="5"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="6"/>
+    </row>
+    <row r="37" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D37" s="5"/>
       <c r="E37" s="5"/>
-      <c r="F37" s="6"/>
-    </row>
-    <row r="38" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C38" s="5"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="6"/>
+    </row>
+    <row r="38" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D38" s="5"/>
       <c r="E38" s="5"/>
-      <c r="F38" s="6"/>
-    </row>
-    <row r="39" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="3"/>
-      <c r="B39" s="3"/>
-      <c r="C39" s="5"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="6"/>
+    </row>
+    <row r="39" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D39" s="5"/>
       <c r="E39" s="5"/>
-      <c r="F39" s="6"/>
-    </row>
-    <row r="40" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="3"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="6"/>
+    </row>
+    <row r="40" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="3"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
-      <c r="F40" s="8"/>
-    </row>
-    <row r="41" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="5"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="6"/>
+    </row>
+    <row r="41" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="3"/>
-      <c r="C41" s="7"/>
+      <c r="C41" s="3"/>
       <c r="D41" s="7"/>
       <c r="E41" s="7"/>
-      <c r="F41" s="8"/>
-    </row>
-    <row r="42" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="3"/>
+      <c r="F41" s="7"/>
+      <c r="G41" s="8"/>
+    </row>
+    <row r="42" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="3"/>
-      <c r="C42" s="5"/>
-      <c r="D42" s="5"/>
-      <c r="E42" s="5"/>
-      <c r="F42" s="6"/>
-    </row>
-    <row r="43" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="3"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="7"/>
+      <c r="E42" s="7"/>
+      <c r="F42" s="7"/>
+      <c r="G42" s="8"/>
+    </row>
+    <row r="43" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="3"/>
-      <c r="C43" s="5"/>
+      <c r="C43" s="3"/>
       <c r="D43" s="5"/>
       <c r="E43" s="5"/>
-      <c r="F43" s="6"/>
-    </row>
-    <row r="44" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C44" s="5"/>
+      <c r="F43" s="5"/>
+      <c r="G43" s="6"/>
+    </row>
+    <row r="44" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
       <c r="D44" s="5"/>
       <c r="E44" s="5"/>
-      <c r="F44" s="6"/>
-    </row>
-    <row r="45" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="3"/>
-      <c r="B45" s="3"/>
-      <c r="C45" s="5"/>
+      <c r="F44" s="5"/>
+      <c r="G44" s="6"/>
+    </row>
+    <row r="45" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D45" s="5"/>
       <c r="E45" s="5"/>
-      <c r="F45" s="6"/>
-    </row>
-    <row r="46" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C46" s="5"/>
+      <c r="F45" s="5"/>
+      <c r="G45" s="6"/>
+    </row>
+    <row r="46" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="3"/>
+      <c r="C46" s="3"/>
       <c r="D46" s="5"/>
       <c r="E46" s="5"/>
-      <c r="F46" s="6"/>
-    </row>
-    <row r="47" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="4"/>
-      <c r="B47" s="4"/>
-      <c r="C47" s="9"/>
-      <c r="D47" s="10"/>
-      <c r="E47" s="10"/>
-      <c r="F47" s="9"/>
-    </row>
-    <row r="48" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="4"/>
+      <c r="F46" s="5"/>
+      <c r="G46" s="6"/>
+    </row>
+    <row r="47" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D47" s="5"/>
+      <c r="E47" s="5"/>
+      <c r="F47" s="5"/>
+      <c r="G47" s="6"/>
+    </row>
+    <row r="48" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="4"/>
-      <c r="C48" s="9"/>
-      <c r="D48" s="10"/>
+      <c r="C48" s="4"/>
+      <c r="D48" s="9"/>
       <c r="E48" s="10"/>
-      <c r="F48" s="9"/>
-    </row>
-    <row r="49" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="4"/>
+      <c r="F48" s="10"/>
+      <c r="G48" s="9"/>
+    </row>
+    <row r="49" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="4"/>
-      <c r="C49" s="9"/>
-      <c r="D49" s="10"/>
+      <c r="C49" s="4"/>
+      <c r="D49" s="9"/>
       <c r="E49" s="10"/>
-      <c r="F49" s="9"/>
-    </row>
-    <row r="50" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="4"/>
+      <c r="F49" s="10"/>
+      <c r="G49" s="9"/>
+    </row>
+    <row r="50" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="4"/>
-      <c r="C50" s="9"/>
-      <c r="D50" s="10"/>
+      <c r="C50" s="4"/>
+      <c r="D50" s="9"/>
       <c r="E50" s="10"/>
-      <c r="F50" s="9"/>
-    </row>
-    <row r="51" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="4"/>
+      <c r="F50" s="10"/>
+      <c r="G50" s="9"/>
+    </row>
+    <row r="51" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="4"/>
-      <c r="C51" s="9"/>
-      <c r="D51" s="10"/>
+      <c r="C51" s="4"/>
+      <c r="D51" s="9"/>
       <c r="E51" s="10"/>
-      <c r="F51" s="9"/>
-    </row>
-    <row r="52" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="4"/>
+      <c r="F51" s="10"/>
+      <c r="G51" s="9"/>
+    </row>
+    <row r="52" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="4"/>
-      <c r="C52" s="9"/>
-      <c r="D52" s="10"/>
+      <c r="C52" s="4"/>
+      <c r="D52" s="9"/>
       <c r="E52" s="10"/>
-      <c r="F52" s="9"/>
-    </row>
-    <row r="53" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C53" s="11"/>
-      <c r="D53" s="11"/>
-      <c r="E53" s="11"/>
-      <c r="F53" s="12"/>
-    </row>
-    <row r="54" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C54" s="5"/>
-      <c r="D54" s="5"/>
-      <c r="E54" s="5"/>
-      <c r="F54" s="6"/>
-    </row>
-    <row r="55" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="3"/>
-      <c r="B55" s="3"/>
-      <c r="C55" s="5"/>
+      <c r="F52" s="10"/>
+      <c r="G52" s="9"/>
+    </row>
+    <row r="53" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="4"/>
+      <c r="C53" s="4"/>
+      <c r="D53" s="9"/>
+      <c r="E53" s="10"/>
+      <c r="F53" s="10"/>
+      <c r="G53" s="9"/>
+    </row>
+    <row r="54" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D54" s="11"/>
+      <c r="E54" s="11"/>
+      <c r="F54" s="11"/>
+      <c r="G54" s="12"/>
+    </row>
+    <row r="55" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D55" s="5"/>
       <c r="E55" s="5"/>
-      <c r="F55" s="6"/>
-    </row>
-    <row r="56" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="13"/>
-      <c r="B56" s="13"/>
-      <c r="C56" s="11"/>
-      <c r="D56" s="11"/>
-      <c r="E56" s="11"/>
-      <c r="F56" s="12"/>
-    </row>
-    <row r="57" spans="1:6" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="4"/>
-      <c r="B57" s="4"/>
-      <c r="C57" s="11"/>
+      <c r="F55" s="5"/>
+      <c r="G55" s="6"/>
+    </row>
+    <row r="56" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B56" s="3"/>
+      <c r="C56" s="3"/>
+      <c r="D56" s="5"/>
+      <c r="E56" s="5"/>
+      <c r="F56" s="5"/>
+      <c r="G56" s="6"/>
+    </row>
+    <row r="57" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B57" s="13"/>
+      <c r="C57" s="13"/>
       <c r="D57" s="11"/>
       <c r="E57" s="11"/>
-      <c r="F57" s="12"/>
-    </row>
-    <row r="58" spans="1:6" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="4"/>
+      <c r="F57" s="11"/>
+      <c r="G57" s="12"/>
+    </row>
+    <row r="58" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="4"/>
-      <c r="C58" s="11"/>
+      <c r="C58" s="4"/>
       <c r="D58" s="11"/>
       <c r="E58" s="11"/>
-      <c r="F58" s="12"/>
-    </row>
-    <row r="59" spans="1:6" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="4"/>
+      <c r="F58" s="11"/>
+      <c r="G58" s="12"/>
+    </row>
+    <row r="59" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="4"/>
-      <c r="C59" s="11"/>
+      <c r="C59" s="4"/>
       <c r="D59" s="11"/>
       <c r="E59" s="11"/>
-      <c r="F59" s="12"/>
-    </row>
-    <row r="60" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="4"/>
+      <c r="F59" s="11"/>
+      <c r="G59" s="12"/>
+    </row>
+    <row r="60" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B60" s="4"/>
-      <c r="C60" s="14"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="14"/>
-      <c r="F60" s="15"/>
-    </row>
-    <row r="61" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C61" s="5"/>
-      <c r="D61" s="5"/>
-      <c r="E61" s="5"/>
-      <c r="F61" s="6"/>
-    </row>
-    <row r="62" spans="1:6" s="16" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="2"/>
-      <c r="B62" s="2"/>
-      <c r="C62" s="5"/>
+      <c r="C60" s="4"/>
+      <c r="D60" s="11"/>
+      <c r="E60" s="11"/>
+      <c r="F60" s="11"/>
+      <c r="G60" s="12"/>
+    </row>
+    <row r="61" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B61" s="4"/>
+      <c r="C61" s="4"/>
+      <c r="D61" s="14"/>
+      <c r="E61" s="14"/>
+      <c r="F61" s="14"/>
+      <c r="G61" s="15"/>
+    </row>
+    <row r="62" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D62" s="5"/>
       <c r="E62" s="5"/>
-      <c r="F62" s="6"/>
-    </row>
-    <row r="63" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C63" s="5"/>
+      <c r="F62" s="5"/>
+      <c r="G62" s="6"/>
+    </row>
+    <row r="63" spans="2:7" s="16" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B63" s="2"/>
+      <c r="C63" s="2"/>
       <c r="D63" s="5"/>
       <c r="E63" s="5"/>
-      <c r="F63" s="6"/>
-    </row>
-    <row r="64" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C64" s="5"/>
+      <c r="F63" s="5"/>
+      <c r="G63" s="6"/>
+    </row>
+    <row r="64" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D64" s="5"/>
       <c r="E64" s="5"/>
-      <c r="F64" s="6"/>
-    </row>
-    <row r="65" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="3"/>
-      <c r="B65" s="3"/>
-      <c r="C65" s="5"/>
+      <c r="F64" s="5"/>
+      <c r="G64" s="6"/>
+    </row>
+    <row r="65" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D65" s="5"/>
       <c r="E65" s="5"/>
-      <c r="F65" s="6"/>
-    </row>
-    <row r="66" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="3"/>
+      <c r="F65" s="5"/>
+      <c r="G65" s="6"/>
+    </row>
+    <row r="66" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B66" s="3"/>
-      <c r="C66" s="11"/>
-      <c r="D66" s="11"/>
-      <c r="E66" s="11"/>
-      <c r="F66" s="12"/>
-    </row>
-    <row r="67" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="3"/>
+      <c r="C66" s="3"/>
+      <c r="D66" s="5"/>
+      <c r="E66" s="5"/>
+      <c r="F66" s="5"/>
+      <c r="G66" s="6"/>
+    </row>
+    <row r="67" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B67" s="3"/>
-      <c r="C67" s="11"/>
+      <c r="C67" s="3"/>
       <c r="D67" s="11"/>
       <c r="E67" s="11"/>
-      <c r="F67" s="12"/>
-    </row>
-    <row r="68" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C68" s="5"/>
-      <c r="D68" s="5"/>
-      <c r="E68" s="5"/>
-      <c r="F68" s="6"/>
-    </row>
-    <row r="69" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C69" s="5"/>
+      <c r="F67" s="11"/>
+      <c r="G67" s="12"/>
+    </row>
+    <row r="68" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B68" s="3"/>
+      <c r="C68" s="3"/>
+      <c r="D68" s="11"/>
+      <c r="E68" s="11"/>
+      <c r="F68" s="11"/>
+      <c r="G68" s="12"/>
+    </row>
+    <row r="69" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D69" s="5"/>
       <c r="E69" s="5"/>
-      <c r="F69" s="6"/>
-    </row>
-    <row r="70" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C70" s="11"/>
-      <c r="D70" s="11"/>
-      <c r="E70" s="11"/>
-      <c r="F70" s="12"/>
-    </row>
-    <row r="71" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C71" s="5"/>
-      <c r="D71" s="5"/>
-      <c r="E71" s="5"/>
-      <c r="F71" s="6"/>
-    </row>
-    <row r="72" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C72" s="5"/>
+      <c r="F69" s="5"/>
+      <c r="G69" s="6"/>
+    </row>
+    <row r="70" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D70" s="5"/>
+      <c r="E70" s="5"/>
+      <c r="F70" s="5"/>
+      <c r="G70" s="6"/>
+    </row>
+    <row r="71" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D71" s="11"/>
+      <c r="E71" s="11"/>
+      <c r="F71" s="11"/>
+      <c r="G71" s="12"/>
+    </row>
+    <row r="72" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D72" s="5"/>
       <c r="E72" s="5"/>
-      <c r="F72" s="6"/>
-    </row>
-    <row r="73" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C73" s="5"/>
+      <c r="F72" s="5"/>
+      <c r="G72" s="6"/>
+    </row>
+    <row r="73" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D73" s="5"/>
       <c r="E73" s="5"/>
-      <c r="F73" s="6"/>
-    </row>
-    <row r="74" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C74" s="5"/>
+      <c r="F73" s="5"/>
+      <c r="G73" s="6"/>
+    </row>
+    <row r="74" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D74" s="5"/>
       <c r="E74" s="5"/>
-      <c r="F74" s="6"/>
-    </row>
-    <row r="75" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="3"/>
-      <c r="B75" s="3"/>
-      <c r="C75" s="5"/>
+      <c r="F74" s="5"/>
+      <c r="G74" s="6"/>
+    </row>
+    <row r="75" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D75" s="5"/>
       <c r="E75" s="5"/>
-      <c r="F75" s="6"/>
-    </row>
-    <row r="76" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="3"/>
+      <c r="F75" s="5"/>
+      <c r="G75" s="6"/>
+    </row>
+    <row r="76" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B76" s="3"/>
-      <c r="C76" s="5"/>
+      <c r="C76" s="3"/>
       <c r="D76" s="5"/>
       <c r="E76" s="5"/>
-      <c r="F76" s="6"/>
-    </row>
-    <row r="77" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="3"/>
+      <c r="F76" s="5"/>
+      <c r="G76" s="6"/>
+    </row>
+    <row r="77" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B77" s="3"/>
-      <c r="C77" s="5"/>
+      <c r="C77" s="3"/>
       <c r="D77" s="5"/>
       <c r="E77" s="5"/>
-      <c r="F77" s="6"/>
-    </row>
-    <row r="78" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C78" s="5"/>
+      <c r="F77" s="5"/>
+      <c r="G77" s="6"/>
+    </row>
+    <row r="78" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B78" s="3"/>
+      <c r="C78" s="3"/>
       <c r="D78" s="5"/>
       <c r="E78" s="5"/>
-      <c r="F78" s="6"/>
-    </row>
-    <row r="79" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C79" s="5"/>
+      <c r="F78" s="5"/>
+      <c r="G78" s="6"/>
+    </row>
+    <row r="79" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D79" s="5"/>
       <c r="E79" s="5"/>
-      <c r="F79" s="6"/>
-    </row>
-    <row r="80" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C80" s="5"/>
+      <c r="F79" s="5"/>
+      <c r="G79" s="6"/>
+    </row>
+    <row r="80" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D80" s="5"/>
       <c r="E80" s="5"/>
-      <c r="F80" s="6"/>
-    </row>
-    <row r="81" spans="3:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C81" s="5"/>
+      <c r="F80" s="5"/>
+      <c r="G80" s="6"/>
+    </row>
+    <row r="81" spans="4:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D81" s="5"/>
       <c r="E81" s="5"/>
-      <c r="F81" s="6"/>
-    </row>
-    <row r="82" spans="3:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C82" s="5"/>
+      <c r="F81" s="5"/>
+      <c r="G81" s="6"/>
+    </row>
+    <row r="82" spans="4:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D82" s="5"/>
       <c r="E82" s="5"/>
-      <c r="F82" s="6"/>
-    </row>
-    <row r="83" spans="3:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C83" s="5"/>
+      <c r="F82" s="5"/>
+      <c r="G82" s="6"/>
+    </row>
+    <row r="83" spans="4:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D83" s="5"/>
       <c r="E83" s="5"/>
-      <c r="F83" s="6"/>
-    </row>
-    <row r="84" spans="3:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C84" s="5"/>
+      <c r="F83" s="5"/>
+      <c r="G83" s="6"/>
+    </row>
+    <row r="84" spans="4:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D84" s="5"/>
       <c r="E84" s="5"/>
-      <c r="F84" s="6"/>
-    </row>
-    <row r="85" spans="3:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C85" s="5"/>
+      <c r="F84" s="5"/>
+      <c r="G84" s="6"/>
+    </row>
+    <row r="85" spans="4:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D85" s="5"/>
       <c r="E85" s="5"/>
-      <c r="F85" s="6"/>
-    </row>
-    <row r="86" spans="3:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C86" s="5"/>
+      <c r="F85" s="5"/>
+      <c r="G85" s="6"/>
+    </row>
+    <row r="86" spans="4:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D86" s="5"/>
       <c r="E86" s="5"/>
-      <c r="F86" s="6"/>
-    </row>
-    <row r="87" spans="3:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C87" s="5"/>
+      <c r="F86" s="5"/>
+      <c r="G86" s="6"/>
+    </row>
+    <row r="87" spans="4:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D87" s="5"/>
       <c r="E87" s="5"/>
-      <c r="F87" s="6"/>
-    </row>
-    <row r="88" spans="3:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C88" s="5"/>
+      <c r="F87" s="5"/>
+      <c r="G87" s="6"/>
+    </row>
+    <row r="88" spans="4:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D88" s="5"/>
       <c r="E88" s="5"/>
-      <c r="F88" s="6"/>
-    </row>
-    <row r="89" spans="3:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C89" s="5"/>
+      <c r="F88" s="5"/>
+      <c r="G88" s="6"/>
+    </row>
+    <row r="89" spans="4:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D89" s="5"/>
       <c r="E89" s="5"/>
-      <c r="F89" s="6"/>
-    </row>
-    <row r="90" spans="3:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C90" s="5"/>
+      <c r="F89" s="5"/>
+      <c r="G89" s="6"/>
+    </row>
+    <row r="90" spans="4:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D90" s="5"/>
       <c r="E90" s="5"/>
-      <c r="F90" s="6"/>
-    </row>
-    <row r="91" spans="3:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C91" s="5"/>
+      <c r="F90" s="5"/>
+      <c r="G90" s="6"/>
+    </row>
+    <row r="91" spans="4:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D91" s="5"/>
       <c r="E91" s="5"/>
-      <c r="F91" s="6"/>
-    </row>
-    <row r="92" spans="3:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C92" s="5"/>
+      <c r="F91" s="5"/>
+      <c r="G91" s="6"/>
+    </row>
+    <row r="92" spans="4:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D92" s="5"/>
       <c r="E92" s="5"/>
-      <c r="F92" s="6"/>
-    </row>
-    <row r="93" spans="3:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C93" s="5"/>
+      <c r="F92" s="5"/>
+      <c r="G92" s="6"/>
+    </row>
+    <row r="93" spans="4:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D93" s="5"/>
       <c r="E93" s="5"/>
-      <c r="F93" s="6"/>
-    </row>
-    <row r="94" spans="3:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C94" s="5"/>
+      <c r="F93" s="5"/>
+      <c r="G93" s="6"/>
+    </row>
+    <row r="94" spans="4:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D94" s="5"/>
       <c r="E94" s="5"/>
-      <c r="F94" s="6"/>
-    </row>
-    <row r="95" spans="3:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C95" s="5"/>
+      <c r="F94" s="5"/>
+      <c r="G94" s="6"/>
+    </row>
+    <row r="95" spans="4:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D95" s="5"/>
       <c r="E95" s="5"/>
-      <c r="F95" s="6"/>
-    </row>
-    <row r="96" spans="3:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C96" s="5"/>
+      <c r="F95" s="5"/>
+      <c r="G95" s="6"/>
+    </row>
+    <row r="96" spans="4:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D96" s="5"/>
       <c r="E96" s="5"/>
-      <c r="F96" s="6"/>
-    </row>
-    <row r="97" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C97" s="5"/>
+      <c r="F96" s="5"/>
+      <c r="G96" s="6"/>
+    </row>
+    <row r="97" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D97" s="5"/>
       <c r="E97" s="5"/>
-      <c r="F97" s="6"/>
-    </row>
-    <row r="98" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="3"/>
-      <c r="B98" s="3"/>
-      <c r="C98" s="11"/>
-      <c r="D98" s="11"/>
-      <c r="E98" s="11"/>
-      <c r="F98" s="12"/>
-    </row>
-    <row r="99" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="3"/>
+      <c r="F97" s="5"/>
+      <c r="G97" s="6"/>
+    </row>
+    <row r="98" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D98" s="5"/>
+      <c r="E98" s="5"/>
+      <c r="F98" s="5"/>
+      <c r="G98" s="6"/>
+    </row>
+    <row r="99" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B99" s="3"/>
-      <c r="C99" s="5"/>
-      <c r="D99" s="5"/>
-      <c r="E99" s="5"/>
-      <c r="F99" s="6"/>
-    </row>
-    <row r="100" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="3"/>
+      <c r="C99" s="3"/>
+      <c r="D99" s="11"/>
+      <c r="E99" s="11"/>
+      <c r="F99" s="11"/>
+      <c r="G99" s="12"/>
+    </row>
+    <row r="100" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B100" s="3"/>
-      <c r="C100" s="5"/>
+      <c r="C100" s="3"/>
       <c r="D100" s="5"/>
       <c r="E100" s="5"/>
-      <c r="F100" s="6"/>
-    </row>
-    <row r="101" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C101" s="5"/>
+      <c r="F100" s="5"/>
+      <c r="G100" s="6"/>
+    </row>
+    <row r="101" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B101" s="3"/>
+      <c r="C101" s="3"/>
       <c r="D101" s="5"/>
       <c r="E101" s="5"/>
-      <c r="F101" s="6"/>
-    </row>
-    <row r="102" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C102" s="5"/>
+      <c r="F101" s="5"/>
+      <c r="G101" s="6"/>
+    </row>
+    <row r="102" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D102" s="5"/>
       <c r="E102" s="5"/>
-      <c r="F102" s="6"/>
-    </row>
-    <row r="103" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="16"/>
-      <c r="B103" s="16"/>
-      <c r="C103" s="5"/>
+      <c r="F102" s="5"/>
+      <c r="G102" s="6"/>
+    </row>
+    <row r="103" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D103" s="5"/>
       <c r="E103" s="5"/>
-      <c r="F103" s="6"/>
-    </row>
-    <row r="104" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C104" s="5"/>
+      <c r="F103" s="5"/>
+      <c r="G103" s="6"/>
+    </row>
+    <row r="104" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B104" s="16"/>
+      <c r="C104" s="16"/>
       <c r="D104" s="5"/>
       <c r="E104" s="5"/>
-      <c r="F104" s="6"/>
+      <c r="F104" s="5"/>
+      <c r="G104" s="6"/>
+    </row>
+    <row r="105" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D105" s="5"/>
+      <c r="E105" s="5"/>
+      <c r="F105" s="5"/>
+      <c r="G105" s="6"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="23" priority="2"/>
+  <conditionalFormatting sqref="D1:D1048576">
+    <cfRule type="duplicateValues" dxfId="5" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -2793,691 +2534,719 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4DEFA5D-C6DF-4BEE-A0BF-87172BA2BD41}">
-  <dimension ref="A1:F95"/>
+  <dimension ref="B1:G96"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24" style="2" customWidth="1"/>
-    <col min="5" max="5" width="30.85546875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="8.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="2.5703125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="6.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24" style="2" customWidth="1"/>
+    <col min="6" max="6" width="30.85546875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="8.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
+    <row r="1" spans="2:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="22" t="s">
+      <c r="C2" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="22" t="s">
+      <c r="D2" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="E2" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="23" t="s">
+      <c r="F2" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="23" t="s">
+      <c r="G2" s="22" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="20">
+    <row r="3" spans="2:7" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3">
         <v>1</v>
       </c>
-      <c r="B2" s="26" t="s">
+      <c r="C3" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="26" t="s">
+      <c r="D3" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="26" t="s">
+      <c r="E3" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="26" t="s">
+      <c r="F3" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="F2" s="27"/>
-    </row>
-    <row r="3" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="20">
+      <c r="G3" s="23"/>
+    </row>
+    <row r="4" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4">
         <v>2</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="C4" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="D4" s="23" t="s">
         <v>84</v>
       </c>
-      <c r="D3" s="26" t="s">
+      <c r="E4" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="E3" s="26" t="s">
+      <c r="F4" s="23" t="s">
         <v>85</v>
       </c>
-      <c r="F3" s="27"/>
-    </row>
-    <row r="4" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="20">
+      <c r="G4" s="23"/>
+    </row>
+    <row r="5" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5">
         <v>3</v>
       </c>
-      <c r="B4" s="26" t="s">
+      <c r="C5" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="D5" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="E5" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="F5" s="23" t="s">
         <v>85</v>
       </c>
-      <c r="F4" s="27"/>
-    </row>
-    <row r="5" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="20">
+      <c r="G5" s="23"/>
+    </row>
+    <row r="6" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6">
         <v>4</v>
       </c>
-      <c r="B5" s="26" t="s">
+      <c r="C6" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="C5" s="26" t="s">
+      <c r="D6" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="D5" s="26" t="s">
+      <c r="E6" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="E5" s="26" t="s">
+      <c r="F6" s="23" t="s">
         <v>85</v>
       </c>
-      <c r="F5" s="27"/>
-    </row>
-    <row r="6" spans="1:6" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="20">
+      <c r="G6" s="23"/>
+    </row>
+    <row r="7" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7">
         <v>5</v>
       </c>
-      <c r="B6" s="30" t="s">
+      <c r="C7" s="24" t="s">
         <v>91</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="D7" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="D6" s="30" t="s">
+      <c r="E7" s="24" t="s">
         <v>93</v>
       </c>
-      <c r="E6" s="30" t="s">
+      <c r="F7" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="F6" s="30">
+      <c r="G7" s="24">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="20">
+    <row r="8" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8">
         <v>6</v>
       </c>
-      <c r="B7" s="30" t="s">
+      <c r="C8" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="C7" s="30" t="s">
+      <c r="D8" s="24" t="s">
         <v>95</v>
       </c>
-      <c r="D7" s="30" t="s">
+      <c r="E8" s="24" t="s">
         <v>93</v>
       </c>
-      <c r="E7" s="30" t="s">
+      <c r="F8" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="F7" s="30">
+      <c r="G8" s="24">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="20">
+    <row r="9" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9">
         <v>7</v>
       </c>
-      <c r="B8" s="26" t="s">
+      <c r="C9" s="23" t="s">
         <v>96</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="D9" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="D8" s="26" t="s">
+      <c r="E9" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="26" t="s">
+      <c r="F9" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="F8" s="27"/>
-    </row>
-    <row r="9" spans="1:6" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="20">
+      <c r="G9" s="23"/>
+    </row>
+    <row r="10" spans="2:7" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10">
         <v>8</v>
       </c>
-      <c r="B9" s="26" t="s">
+      <c r="C10" s="23" t="s">
         <v>99</v>
       </c>
-      <c r="C9" s="30" t="s">
+      <c r="D10" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="D9" s="26" t="s">
+      <c r="E10" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="E9" s="30" t="s">
+      <c r="F10" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="F9" s="27"/>
-    </row>
-    <row r="10" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="6"/>
-    </row>
-    <row r="11" spans="1:6" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="6"/>
-    </row>
-    <row r="12" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="8"/>
-    </row>
-    <row r="13" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="6"/>
-    </row>
-    <row r="14" spans="1:6" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="5"/>
+      <c r="G10" s="23"/>
+    </row>
+    <row r="11" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11">
+        <v>9</v>
+      </c>
+      <c r="C11" s="23" t="s">
+        <v>102</v>
+      </c>
+      <c r="D11" s="23" t="s">
+        <v>103</v>
+      </c>
+      <c r="E11" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="F11" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="G11" s="25"/>
+    </row>
+    <row r="12" spans="2:7" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12">
+        <v>10</v>
+      </c>
+      <c r="C12" s="23" t="s">
+        <v>105</v>
+      </c>
+      <c r="D12" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="E12" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="F12" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="G12" s="25"/>
+    </row>
+    <row r="13" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="8"/>
+    </row>
+    <row r="14" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
-      <c r="F14" s="6"/>
-    </row>
-    <row r="15" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="6"/>
+    </row>
+    <row r="15" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
-      <c r="F15" s="6"/>
-    </row>
-    <row r="16" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C16" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="6"/>
+    </row>
+    <row r="16" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
-      <c r="F16" s="6"/>
-    </row>
-    <row r="17" spans="1:6" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="6"/>
+    </row>
+    <row r="17" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
-      <c r="F17" s="6"/>
-    </row>
-    <row r="18" spans="1:6" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C18" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="6"/>
+    </row>
+    <row r="18" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
-      <c r="F18" s="6"/>
-    </row>
-    <row r="19" spans="1:6" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="8"/>
-    </row>
-    <row r="20" spans="1:6" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C20" s="7"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="6"/>
+    </row>
+    <row r="19" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="6"/>
+    </row>
+    <row r="20" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
-      <c r="F20" s="8"/>
-    </row>
-    <row r="21" spans="1:6" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="6"/>
-    </row>
-    <row r="22" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="3"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="5"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="8"/>
+    </row>
+    <row r="21" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="8"/>
+    </row>
+    <row r="22" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
-      <c r="F22" s="6"/>
-    </row>
-    <row r="23" spans="1:6" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="6"/>
+    </row>
+    <row r="23" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
-      <c r="F23" s="6"/>
-    </row>
-    <row r="24" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="3"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="6"/>
+    </row>
+    <row r="24" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
       <c r="D24" s="5"/>
       <c r="E24" s="5"/>
-      <c r="F24" s="6"/>
-    </row>
-    <row r="25" spans="1:6" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="6"/>
+    </row>
+    <row r="25" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
-      <c r="F25" s="6"/>
-    </row>
-    <row r="26" spans="1:6" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="9"/>
-    </row>
-    <row r="27" spans="1:6" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C27" s="9"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="6"/>
+    </row>
+    <row r="26" spans="2:7" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="6"/>
+    </row>
+    <row r="27" spans="2:7" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D27" s="9"/>
-      <c r="E27" s="10"/>
-      <c r="F27" s="9"/>
-    </row>
-    <row r="28" spans="1:6" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C28" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="10"/>
+      <c r="G27" s="9"/>
+    </row>
+    <row r="28" spans="2:7" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D28" s="9"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="9"/>
-    </row>
-    <row r="29" spans="1:6" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C29" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="9"/>
+    </row>
+    <row r="29" spans="2:7" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D29" s="9"/>
-      <c r="E29" s="10"/>
-      <c r="F29" s="9"/>
-    </row>
-    <row r="30" spans="1:6" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C30" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="9"/>
+    </row>
+    <row r="30" spans="2:7" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D30" s="9"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="9"/>
-    </row>
-    <row r="31" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="4"/>
-      <c r="B31" s="4"/>
-      <c r="C31" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="10"/>
+      <c r="G30" s="9"/>
+    </row>
+    <row r="31" spans="2:7" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D31" s="9"/>
-      <c r="E31" s="10"/>
-      <c r="F31" s="9"/>
-    </row>
-    <row r="32" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C32" s="11"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="12"/>
-    </row>
-    <row r="33" spans="1:6" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
-      <c r="C33" s="5"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="6"/>
-    </row>
-    <row r="34" spans="1:6" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="3"/>
-      <c r="B34" s="3"/>
-      <c r="C34" s="5"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="10"/>
+      <c r="G31" s="9"/>
+    </row>
+    <row r="32" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="10"/>
+      <c r="G32" s="9"/>
+    </row>
+    <row r="33" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="12"/>
+    </row>
+    <row r="34" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
       <c r="D34" s="5"/>
       <c r="E34" s="5"/>
-      <c r="F34" s="6"/>
-    </row>
-    <row r="35" spans="1:6" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="13"/>
-      <c r="B35" s="13"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="12"/>
-    </row>
-    <row r="36" spans="1:6" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C36" s="11"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="6"/>
+    </row>
+    <row r="35" spans="2:7" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="6"/>
+    </row>
+    <row r="36" spans="2:7" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="13"/>
+      <c r="C36" s="13"/>
       <c r="D36" s="11"/>
       <c r="E36" s="11"/>
-      <c r="F36" s="12"/>
-    </row>
-    <row r="37" spans="1:6" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C37" s="11"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="12"/>
+    </row>
+    <row r="37" spans="2:7" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D37" s="11"/>
       <c r="E37" s="11"/>
-      <c r="F37" s="12"/>
-    </row>
-    <row r="38" spans="1:6" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C38" s="11"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="12"/>
+    </row>
+    <row r="38" spans="2:7" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D38" s="11"/>
       <c r="E38" s="11"/>
-      <c r="F38" s="12"/>
-    </row>
-    <row r="39" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="4"/>
-      <c r="B39" s="4"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="15"/>
-    </row>
-    <row r="40" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C40" s="5"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="6"/>
-    </row>
-    <row r="41" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C41" s="5"/>
+      <c r="F38" s="11"/>
+      <c r="G38" s="12"/>
+    </row>
+    <row r="39" spans="2:7" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
+      <c r="F39" s="11"/>
+      <c r="G39" s="12"/>
+    </row>
+    <row r="40" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="14"/>
+      <c r="E40" s="14"/>
+      <c r="F40" s="14"/>
+      <c r="G40" s="15"/>
+    </row>
+    <row r="41" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D41" s="5"/>
       <c r="E41" s="5"/>
-      <c r="F41" s="6"/>
-    </row>
-    <row r="42" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C42" s="5"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="6"/>
+    </row>
+    <row r="42" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D42" s="5"/>
       <c r="E42" s="5"/>
-      <c r="F42" s="6"/>
-    </row>
-    <row r="43" spans="1:6" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="2"/>
-      <c r="B43" s="2"/>
-      <c r="C43" s="5"/>
+      <c r="F42" s="5"/>
+      <c r="G42" s="6"/>
+    </row>
+    <row r="43" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D43" s="5"/>
       <c r="E43" s="5"/>
-      <c r="F43" s="6"/>
-    </row>
-    <row r="44" spans="1:6" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C44" s="5"/>
+      <c r="F43" s="5"/>
+      <c r="G43" s="6"/>
+    </row>
+    <row r="44" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
       <c r="D44" s="5"/>
       <c r="E44" s="5"/>
-      <c r="F44" s="6"/>
-    </row>
-    <row r="45" spans="1:6" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C45" s="11"/>
-      <c r="D45" s="11"/>
-      <c r="E45" s="11"/>
-      <c r="F45" s="12"/>
-    </row>
-    <row r="46" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="3"/>
-      <c r="B46" s="3"/>
-      <c r="C46" s="11"/>
+      <c r="F44" s="5"/>
+      <c r="G44" s="6"/>
+    </row>
+    <row r="45" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D45" s="5"/>
+      <c r="E45" s="5"/>
+      <c r="F45" s="5"/>
+      <c r="G45" s="6"/>
+    </row>
+    <row r="46" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D46" s="11"/>
       <c r="E46" s="11"/>
-      <c r="F46" s="12"/>
-    </row>
-    <row r="47" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C47" s="5"/>
-      <c r="D47" s="5"/>
-      <c r="E47" s="5"/>
-      <c r="F47" s="6"/>
-    </row>
-    <row r="48" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C48" s="5"/>
+      <c r="F46" s="11"/>
+      <c r="G46" s="12"/>
+    </row>
+    <row r="47" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B47" s="3"/>
+      <c r="C47" s="3"/>
+      <c r="D47" s="11"/>
+      <c r="E47" s="11"/>
+      <c r="F47" s="11"/>
+      <c r="G47" s="12"/>
+    </row>
+    <row r="48" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D48" s="5"/>
       <c r="E48" s="5"/>
-      <c r="F48" s="6"/>
-    </row>
-    <row r="49" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C49" s="11"/>
-      <c r="D49" s="11"/>
-      <c r="E49" s="11"/>
-      <c r="F49" s="12"/>
-    </row>
-    <row r="50" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C50" s="5"/>
-      <c r="D50" s="5"/>
-      <c r="E50" s="5"/>
-      <c r="F50" s="6"/>
-    </row>
-    <row r="51" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C51" s="5"/>
+      <c r="F48" s="5"/>
+      <c r="G48" s="6"/>
+    </row>
+    <row r="49" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D49" s="5"/>
+      <c r="E49" s="5"/>
+      <c r="F49" s="5"/>
+      <c r="G49" s="6"/>
+    </row>
+    <row r="50" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D50" s="11"/>
+      <c r="E50" s="11"/>
+      <c r="F50" s="11"/>
+      <c r="G50" s="12"/>
+    </row>
+    <row r="51" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D51" s="5"/>
       <c r="E51" s="5"/>
-      <c r="F51" s="6"/>
-    </row>
-    <row r="52" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C52" s="5"/>
+      <c r="F51" s="5"/>
+      <c r="G51" s="6"/>
+    </row>
+    <row r="52" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D52" s="5"/>
       <c r="E52" s="5"/>
-      <c r="F52" s="6"/>
-    </row>
-    <row r="53" spans="1:6" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="2"/>
-      <c r="B53" s="2"/>
-      <c r="C53" s="5"/>
+      <c r="F52" s="5"/>
+      <c r="G52" s="6"/>
+    </row>
+    <row r="53" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D53" s="5"/>
       <c r="E53" s="5"/>
-      <c r="F53" s="6"/>
-    </row>
-    <row r="54" spans="1:6" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C54" s="5"/>
+      <c r="F53" s="5"/>
+      <c r="G53" s="6"/>
+    </row>
+    <row r="54" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="2"/>
+      <c r="C54" s="2"/>
       <c r="D54" s="5"/>
       <c r="E54" s="5"/>
-      <c r="F54" s="6"/>
-    </row>
-    <row r="55" spans="1:6" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C55" s="5"/>
+      <c r="F54" s="5"/>
+      <c r="G54" s="6"/>
+    </row>
+    <row r="55" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D55" s="5"/>
       <c r="E55" s="5"/>
-      <c r="F55" s="6"/>
-    </row>
-    <row r="56" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="3"/>
-      <c r="B56" s="3"/>
-      <c r="C56" s="5"/>
+      <c r="F55" s="5"/>
+      <c r="G55" s="6"/>
+    </row>
+    <row r="56" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D56" s="5"/>
       <c r="E56" s="5"/>
-      <c r="F56" s="6"/>
-    </row>
-    <row r="57" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C57" s="5"/>
+      <c r="F56" s="5"/>
+      <c r="G56" s="6"/>
+    </row>
+    <row r="57" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B57" s="3"/>
+      <c r="C57" s="3"/>
       <c r="D57" s="5"/>
       <c r="E57" s="5"/>
-      <c r="F57" s="6"/>
-    </row>
-    <row r="58" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C58" s="5"/>
+      <c r="F57" s="5"/>
+      <c r="G57" s="6"/>
+    </row>
+    <row r="58" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D58" s="5"/>
       <c r="E58" s="5"/>
-      <c r="F58" s="6"/>
-    </row>
-    <row r="59" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C59" s="5"/>
+      <c r="F58" s="5"/>
+      <c r="G58" s="6"/>
+    </row>
+    <row r="59" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D59" s="5"/>
       <c r="E59" s="5"/>
-      <c r="F59" s="6"/>
-    </row>
-    <row r="60" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C60" s="5"/>
+      <c r="F59" s="5"/>
+      <c r="G59" s="6"/>
+    </row>
+    <row r="60" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D60" s="5"/>
       <c r="E60" s="5"/>
-      <c r="F60" s="6"/>
-    </row>
-    <row r="61" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C61" s="5"/>
+      <c r="F60" s="5"/>
+      <c r="G60" s="6"/>
+    </row>
+    <row r="61" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D61" s="5"/>
       <c r="E61" s="5"/>
-      <c r="F61" s="6"/>
-    </row>
-    <row r="62" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C62" s="5"/>
+      <c r="F61" s="5"/>
+      <c r="G61" s="6"/>
+    </row>
+    <row r="62" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D62" s="5"/>
       <c r="E62" s="5"/>
-      <c r="F62" s="6"/>
-    </row>
-    <row r="63" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C63" s="5"/>
+      <c r="F62" s="5"/>
+      <c r="G62" s="6"/>
+    </row>
+    <row r="63" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D63" s="5"/>
       <c r="E63" s="5"/>
-      <c r="F63" s="6"/>
-    </row>
-    <row r="64" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C64" s="5"/>
+      <c r="F63" s="5"/>
+      <c r="G63" s="6"/>
+    </row>
+    <row r="64" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D64" s="5"/>
       <c r="E64" s="5"/>
-      <c r="F64" s="6"/>
-    </row>
-    <row r="65" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C65" s="5"/>
+      <c r="F64" s="5"/>
+      <c r="G64" s="6"/>
+    </row>
+    <row r="65" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D65" s="5"/>
       <c r="E65" s="5"/>
-      <c r="F65" s="6"/>
-    </row>
-    <row r="66" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C66" s="5"/>
+      <c r="F65" s="5"/>
+      <c r="G65" s="6"/>
+    </row>
+    <row r="66" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D66" s="5"/>
       <c r="E66" s="5"/>
-      <c r="F66" s="6"/>
-    </row>
-    <row r="67" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C67" s="5"/>
+      <c r="F66" s="5"/>
+      <c r="G66" s="6"/>
+    </row>
+    <row r="67" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D67" s="5"/>
       <c r="E67" s="5"/>
-      <c r="F67" s="6"/>
-    </row>
-    <row r="68" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C68" s="5"/>
+      <c r="F67" s="5"/>
+      <c r="G67" s="6"/>
+    </row>
+    <row r="68" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D68" s="5"/>
       <c r="E68" s="5"/>
-      <c r="F68" s="6"/>
-    </row>
-    <row r="69" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C69" s="5"/>
+      <c r="F68" s="5"/>
+      <c r="G68" s="6"/>
+    </row>
+    <row r="69" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D69" s="5"/>
       <c r="E69" s="5"/>
-      <c r="F69" s="6"/>
-    </row>
-    <row r="70" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C70" s="5"/>
+      <c r="F69" s="5"/>
+      <c r="G69" s="6"/>
+    </row>
+    <row r="70" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D70" s="5"/>
       <c r="E70" s="5"/>
-      <c r="F70" s="6"/>
-    </row>
-    <row r="71" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C71" s="5"/>
+      <c r="F70" s="5"/>
+      <c r="G70" s="6"/>
+    </row>
+    <row r="71" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D71" s="5"/>
       <c r="E71" s="5"/>
-      <c r="F71" s="6"/>
-    </row>
-    <row r="72" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C72" s="5"/>
+      <c r="F71" s="5"/>
+      <c r="G71" s="6"/>
+    </row>
+    <row r="72" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D72" s="5"/>
       <c r="E72" s="5"/>
-      <c r="F72" s="6"/>
-    </row>
-    <row r="73" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C73" s="5"/>
+      <c r="F72" s="5"/>
+      <c r="G72" s="6"/>
+    </row>
+    <row r="73" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D73" s="5"/>
       <c r="E73" s="5"/>
-      <c r="F73" s="6"/>
-    </row>
-    <row r="74" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C74" s="5"/>
+      <c r="F73" s="5"/>
+      <c r="G73" s="6"/>
+    </row>
+    <row r="74" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D74" s="5"/>
       <c r="E74" s="5"/>
-      <c r="F74" s="6"/>
-    </row>
-    <row r="75" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C75" s="5"/>
+      <c r="F74" s="5"/>
+      <c r="G74" s="6"/>
+    </row>
+    <row r="75" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D75" s="5"/>
       <c r="E75" s="5"/>
-      <c r="F75" s="6"/>
-    </row>
-    <row r="76" spans="1:6" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="2"/>
-      <c r="B76" s="2"/>
-      <c r="C76" s="5"/>
+      <c r="F75" s="5"/>
+      <c r="G75" s="6"/>
+    </row>
+    <row r="76" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D76" s="5"/>
       <c r="E76" s="5"/>
-      <c r="F76" s="6"/>
-    </row>
-    <row r="77" spans="1:6" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C77" s="11"/>
-      <c r="D77" s="11"/>
-      <c r="E77" s="11"/>
-      <c r="F77" s="12"/>
-    </row>
-    <row r="78" spans="1:6" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C78" s="5"/>
-      <c r="D78" s="5"/>
-      <c r="E78" s="5"/>
-      <c r="F78" s="6"/>
-    </row>
-    <row r="79" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="3"/>
-      <c r="B79" s="3"/>
-      <c r="C79" s="5"/>
+      <c r="F76" s="5"/>
+      <c r="G76" s="6"/>
+    </row>
+    <row r="77" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
+      <c r="D77" s="5"/>
+      <c r="E77" s="5"/>
+      <c r="F77" s="5"/>
+      <c r="G77" s="6"/>
+    </row>
+    <row r="78" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D78" s="11"/>
+      <c r="E78" s="11"/>
+      <c r="F78" s="11"/>
+      <c r="G78" s="12"/>
+    </row>
+    <row r="79" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D79" s="5"/>
       <c r="E79" s="5"/>
-      <c r="F79" s="6"/>
-    </row>
-    <row r="80" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C80" s="5"/>
+      <c r="F79" s="5"/>
+      <c r="G79" s="6"/>
+    </row>
+    <row r="80" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B80" s="3"/>
+      <c r="C80" s="3"/>
       <c r="D80" s="5"/>
       <c r="E80" s="5"/>
-      <c r="F80" s="6"/>
-    </row>
-    <row r="81" spans="1:6" s="16" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="2"/>
-      <c r="B81" s="2"/>
-      <c r="C81" s="5"/>
+      <c r="F80" s="5"/>
+      <c r="G80" s="6"/>
+    </row>
+    <row r="81" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D81" s="5"/>
       <c r="E81" s="5"/>
-      <c r="F81" s="6"/>
-    </row>
-    <row r="82" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="16"/>
-      <c r="B82" s="16"/>
-      <c r="C82" s="5"/>
+      <c r="F81" s="5"/>
+      <c r="G81" s="6"/>
+    </row>
+    <row r="82" spans="2:7" s="16" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B82" s="2"/>
+      <c r="C82" s="2"/>
       <c r="D82" s="5"/>
       <c r="E82" s="5"/>
-      <c r="F82" s="6"/>
-    </row>
-    <row r="83" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C83" s="5"/>
+      <c r="F82" s="5"/>
+      <c r="G82" s="6"/>
+    </row>
+    <row r="83" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B83" s="16"/>
+      <c r="C83" s="16"/>
       <c r="D83" s="5"/>
       <c r="E83" s="5"/>
-      <c r="F83" s="6"/>
-    </row>
-    <row r="84" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="F83" s="5"/>
+      <c r="G83" s="6"/>
+    </row>
+    <row r="84" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D84" s="5"/>
+      <c r="E84" s="5"/>
+      <c r="F84" s="5"/>
+      <c r="G84" s="6"/>
+    </row>
+    <row r="85" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <conditionalFormatting sqref="C2:C9">
-    <cfRule type="duplicateValues" dxfId="12" priority="1"/>
+  <conditionalFormatting sqref="D3:D12">
+    <cfRule type="duplicateValues" dxfId="4" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C10:D1048576 C1">
-    <cfRule type="duplicateValues" dxfId="11" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="6"/>
+  <conditionalFormatting sqref="D11">
+    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D11:D12">
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D13:E1048576 D2">
+    <cfRule type="duplicateValues" dxfId="1" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>

--- a/IA_CCBS_BANK_SIDE/AccountOther/LoanAccountOpening_InstantProcess.xlsx
+++ b/IA_CCBS_BANK_SIDE/AccountOther/LoanAccountOpening_InstantProcess.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sw\Relational_Files\iApply\Interfaces\Interfaces_plus_allbanks\IA_CCBS_BANK_SIDE\AccountOther\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kmilos\source\repos\iApply_CCBS_API\IA_CCBS_BANK_SIDE\AccountOther\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E31733D-87A5-434A-9D65-671FA85B02E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4234C863-96FE-4972-B220-969F8E23A493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-5550" windowWidth="30960" windowHeight="16920" xr2:uid="{68F28061-2ECD-4B0A-AB1D-3A449686159F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{68F28061-2ECD-4B0A-AB1D-3A449686159F}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="3" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="112">
   <si>
     <t>Description</t>
   </si>
@@ -352,6 +352,21 @@
   </si>
   <si>
     <t>iban_account_cd</t>
+  </si>
+  <si>
+    <t>MarginFixedIR</t>
+  </si>
+  <si>
+    <t>MarginFloatingIR</t>
+  </si>
+  <si>
+    <t>FloatingLocal</t>
+  </si>
+  <si>
+    <t>decimal (19,2)</t>
+  </si>
+  <si>
+    <t>string</t>
   </si>
 </sst>
 </file>
@@ -520,7 +535,7 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -599,6 +614,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="20% - Accent4" xfId="1" builtinId="42"/>
@@ -1026,7 +1042,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A6ACF92C-1104-4C93-8F8B-A938A4312D3B}" name="Table2" displayName="Table2" ref="B2:G31" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20" headerRowCellStyle="Normal" dataCellStyle="Normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A6ACF92C-1104-4C93-8F8B-A938A4312D3B}" name="Table2" displayName="Table2" ref="B2:G34" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20" headerRowCellStyle="Normal" dataCellStyle="Normal">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:G31">
     <sortCondition ref="B3"/>
   </sortState>
@@ -1355,20 +1371,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BB8ACDA-C8F4-4728-9499-8B46BAA74AEA}">
   <dimension ref="B2:C14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.5703125" customWidth="1"/>
-    <col min="2" max="2" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.5546875" customWidth="1"/>
+    <col min="2" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:3" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="17"/>
       <c r="C2" s="18" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B3" s="18" t="s">
         <v>10</v>
       </c>
@@ -1376,7 +1392,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B4" s="18" t="s">
         <v>12</v>
       </c>
@@ -1384,7 +1400,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B5" s="18" t="s">
         <v>13</v>
       </c>
@@ -1392,7 +1408,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B6" s="21" t="s">
         <v>21</v>
       </c>
@@ -1400,7 +1416,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B7" s="18" t="s">
         <v>15</v>
       </c>
@@ -1408,11 +1424,11 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B8" s="18"/>
       <c r="C8" s="19"/>
     </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B9" s="18" t="s">
         <v>17</v>
       </c>
@@ -1420,7 +1436,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B10" s="18" t="s">
         <v>19</v>
       </c>
@@ -1428,15 +1444,15 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B11" s="18"/>
       <c r="C11" s="19"/>
     </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B12" s="18"/>
       <c r="C12" s="19"/>
     </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B13" s="18" t="s">
         <v>20</v>
       </c>
@@ -1444,7 +1460,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B14" s="18"/>
       <c r="C14" s="19"/>
     </row>
@@ -1456,20 +1472,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03AC1DB5-1548-45C4-B0E5-7097191C5328}">
   <dimension ref="B1:G105"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="1.42578125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="6.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="30.85546875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.85546875" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="1.44140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="6.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.88671875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="19.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.88671875" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="22" t="s">
         <v>8</v>
       </c>
@@ -1489,7 +1505,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="2:7" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:7" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3">
         <v>1</v>
       </c>
@@ -1507,7 +1523,7 @@
       </c>
       <c r="G3" s="26"/>
     </row>
-    <row r="4" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4">
         <v>2</v>
       </c>
@@ -1525,7 +1541,7 @@
       </c>
       <c r="G4" s="26"/>
     </row>
-    <row r="5" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>3</v>
       </c>
@@ -1543,7 +1559,7 @@
       </c>
       <c r="G5" s="26"/>
     </row>
-    <row r="6" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>4</v>
       </c>
@@ -1561,7 +1577,7 @@
       </c>
       <c r="G6" s="26"/>
     </row>
-    <row r="7" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>5</v>
       </c>
@@ -1579,7 +1595,7 @@
       </c>
       <c r="G7" s="26"/>
     </row>
-    <row r="8" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8">
         <v>6</v>
       </c>
@@ -1597,7 +1613,7 @@
       </c>
       <c r="G8" s="27"/>
     </row>
-    <row r="9" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9">
         <v>7</v>
       </c>
@@ -1615,7 +1631,7 @@
       </c>
       <c r="G9" s="26"/>
     </row>
-    <row r="10" spans="2:7" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:7" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10">
         <v>8</v>
       </c>
@@ -1633,7 +1649,7 @@
       </c>
       <c r="G10" s="27"/>
     </row>
-    <row r="11" spans="2:7" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:7" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11">
         <v>9</v>
       </c>
@@ -1651,7 +1667,7 @@
       </c>
       <c r="G11" s="26"/>
     </row>
-    <row r="12" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12">
         <v>10</v>
       </c>
@@ -1669,7 +1685,7 @@
       </c>
       <c r="G12" s="26"/>
     </row>
-    <row r="13" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13">
         <v>11</v>
       </c>
@@ -1687,7 +1703,7 @@
       </c>
       <c r="G13" s="26"/>
     </row>
-    <row r="14" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14">
         <v>12</v>
       </c>
@@ -1705,7 +1721,7 @@
       </c>
       <c r="G14" s="26"/>
     </row>
-    <row r="15" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15">
         <v>13</v>
       </c>
@@ -1723,7 +1739,7 @@
       </c>
       <c r="G15" s="26"/>
     </row>
-    <row r="16" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16">
         <v>14</v>
       </c>
@@ -1741,7 +1757,7 @@
       </c>
       <c r="G16" s="26"/>
     </row>
-    <row r="17" spans="2:7" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:7" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17">
         <v>15</v>
       </c>
@@ -1759,7 +1775,7 @@
       </c>
       <c r="G17" s="26"/>
     </row>
-    <row r="18" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18">
         <v>16</v>
       </c>
@@ -1777,7 +1793,7 @@
       </c>
       <c r="G18" s="26"/>
     </row>
-    <row r="19" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19">
         <v>17</v>
       </c>
@@ -1795,7 +1811,7 @@
       </c>
       <c r="G19" s="26"/>
     </row>
-    <row r="20" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20">
         <v>18</v>
       </c>
@@ -1813,7 +1829,7 @@
       </c>
       <c r="G20" s="26"/>
     </row>
-    <row r="21" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21">
         <v>19</v>
       </c>
@@ -1831,7 +1847,7 @@
       </c>
       <c r="G21" s="26"/>
     </row>
-    <row r="22" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22">
         <v>20</v>
       </c>
@@ -1849,7 +1865,7 @@
       </c>
       <c r="G22" s="26"/>
     </row>
-    <row r="23" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23">
         <v>21</v>
       </c>
@@ -1867,7 +1883,7 @@
       </c>
       <c r="G23" s="26"/>
     </row>
-    <row r="24" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24">
         <v>22</v>
       </c>
@@ -1885,7 +1901,7 @@
       </c>
       <c r="G24" s="26"/>
     </row>
-    <row r="25" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25">
         <v>23</v>
       </c>
@@ -1903,7 +1919,7 @@
       </c>
       <c r="G25" s="26"/>
     </row>
-    <row r="26" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26">
         <v>24</v>
       </c>
@@ -1921,7 +1937,7 @@
       </c>
       <c r="G26" s="26"/>
     </row>
-    <row r="27" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27">
         <v>25</v>
       </c>
@@ -1939,7 +1955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28">
         <v>26</v>
       </c>
@@ -1957,7 +1973,7 @@
       </c>
       <c r="G28" s="27"/>
     </row>
-    <row r="29" spans="2:7" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:7" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29">
         <v>27</v>
       </c>
@@ -1975,7 +1991,7 @@
       </c>
       <c r="G29" s="26"/>
     </row>
-    <row r="30" spans="2:7" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:7" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30">
         <v>28</v>
       </c>
@@ -1993,7 +2009,7 @@
       </c>
       <c r="G30" s="26"/>
     </row>
-    <row r="31" spans="2:7" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:7" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31">
         <v>29</v>
       </c>
@@ -2011,29 +2027,61 @@
       </c>
       <c r="G31" s="26"/>
     </row>
-    <row r="32" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="5"/>
-      <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
-      <c r="G32" s="6"/>
-    </row>
-    <row r="33" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D33" s="5"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="6"/>
-    </row>
-    <row r="34" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="7"/>
-      <c r="G34" s="8"/>
-    </row>
-    <row r="35" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B32">
+        <v>30</v>
+      </c>
+      <c r="C32" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="D32" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="E32" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="F32" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="G32" s="28"/>
+    </row>
+    <row r="33" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B33">
+        <v>31</v>
+      </c>
+      <c r="C33" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="D33" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="E33" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="F33" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="G33" s="28"/>
+    </row>
+    <row r="34" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B34">
+        <v>32</v>
+      </c>
+      <c r="C34" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="D34" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="E34" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="F34" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="G34" s="28"/>
+    </row>
+    <row r="35" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
       <c r="D35" s="5"/>
@@ -2041,7 +2089,7 @@
       <c r="F35" s="5"/>
       <c r="G35" s="6"/>
     </row>
-    <row r="36" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
       <c r="D36" s="5"/>
@@ -2049,25 +2097,25 @@
       <c r="F36" s="5"/>
       <c r="G36" s="6"/>
     </row>
-    <row r="37" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D37" s="5"/>
       <c r="E37" s="5"/>
       <c r="F37" s="5"/>
       <c r="G37" s="6"/>
     </row>
-    <row r="38" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D38" s="5"/>
       <c r="E38" s="5"/>
       <c r="F38" s="5"/>
       <c r="G38" s="6"/>
     </row>
-    <row r="39" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D39" s="5"/>
       <c r="E39" s="5"/>
       <c r="F39" s="5"/>
       <c r="G39" s="6"/>
     </row>
-    <row r="40" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
       <c r="D40" s="5"/>
@@ -2075,7 +2123,7 @@
       <c r="F40" s="5"/>
       <c r="G40" s="6"/>
     </row>
-    <row r="41" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
       <c r="D41" s="7"/>
@@ -2083,7 +2131,7 @@
       <c r="F41" s="7"/>
       <c r="G41" s="8"/>
     </row>
-    <row r="42" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
       <c r="D42" s="7"/>
@@ -2091,7 +2139,7 @@
       <c r="F42" s="7"/>
       <c r="G42" s="8"/>
     </row>
-    <row r="43" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
       <c r="D43" s="5"/>
@@ -2099,7 +2147,7 @@
       <c r="F43" s="5"/>
       <c r="G43" s="6"/>
     </row>
-    <row r="44" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
       <c r="D44" s="5"/>
@@ -2107,13 +2155,13 @@
       <c r="F44" s="5"/>
       <c r="G44" s="6"/>
     </row>
-    <row r="45" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D45" s="5"/>
       <c r="E45" s="5"/>
       <c r="F45" s="5"/>
       <c r="G45" s="6"/>
     </row>
-    <row r="46" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
       <c r="D46" s="5"/>
@@ -2121,13 +2169,13 @@
       <c r="F46" s="5"/>
       <c r="G46" s="6"/>
     </row>
-    <row r="47" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D47" s="5"/>
       <c r="E47" s="5"/>
       <c r="F47" s="5"/>
       <c r="G47" s="6"/>
     </row>
-    <row r="48" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
       <c r="D48" s="9"/>
@@ -2135,7 +2183,7 @@
       <c r="F48" s="10"/>
       <c r="G48" s="9"/>
     </row>
-    <row r="49" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
       <c r="D49" s="9"/>
@@ -2143,7 +2191,7 @@
       <c r="F49" s="10"/>
       <c r="G49" s="9"/>
     </row>
-    <row r="50" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
       <c r="D50" s="9"/>
@@ -2151,7 +2199,7 @@
       <c r="F50" s="10"/>
       <c r="G50" s="9"/>
     </row>
-    <row r="51" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
       <c r="D51" s="9"/>
@@ -2159,7 +2207,7 @@
       <c r="F51" s="10"/>
       <c r="G51" s="9"/>
     </row>
-    <row r="52" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
       <c r="D52" s="9"/>
@@ -2167,7 +2215,7 @@
       <c r="F52" s="10"/>
       <c r="G52" s="9"/>
     </row>
-    <row r="53" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
       <c r="D53" s="9"/>
@@ -2175,19 +2223,19 @@
       <c r="F53" s="10"/>
       <c r="G53" s="9"/>
     </row>
-    <row r="54" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D54" s="11"/>
       <c r="E54" s="11"/>
       <c r="F54" s="11"/>
       <c r="G54" s="12"/>
     </row>
-    <row r="55" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D55" s="5"/>
       <c r="E55" s="5"/>
       <c r="F55" s="5"/>
       <c r="G55" s="6"/>
     </row>
-    <row r="56" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
       <c r="D56" s="5"/>
@@ -2195,7 +2243,7 @@
       <c r="F56" s="5"/>
       <c r="G56" s="6"/>
     </row>
-    <row r="57" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B57" s="13"/>
       <c r="C57" s="13"/>
       <c r="D57" s="11"/>
@@ -2203,7 +2251,7 @@
       <c r="F57" s="11"/>
       <c r="G57" s="12"/>
     </row>
-    <row r="58" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
       <c r="D58" s="11"/>
@@ -2211,7 +2259,7 @@
       <c r="F58" s="11"/>
       <c r="G58" s="12"/>
     </row>
-    <row r="59" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
       <c r="D59" s="11"/>
@@ -2219,7 +2267,7 @@
       <c r="F59" s="11"/>
       <c r="G59" s="12"/>
     </row>
-    <row r="60" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
       <c r="D60" s="11"/>
@@ -2227,7 +2275,7 @@
       <c r="F60" s="11"/>
       <c r="G60" s="12"/>
     </row>
-    <row r="61" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B61" s="4"/>
       <c r="C61" s="4"/>
       <c r="D61" s="14"/>
@@ -2235,13 +2283,13 @@
       <c r="F61" s="14"/>
       <c r="G61" s="15"/>
     </row>
-    <row r="62" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D62" s="5"/>
       <c r="E62" s="5"/>
       <c r="F62" s="5"/>
       <c r="G62" s="6"/>
     </row>
-    <row r="63" spans="2:7" s="16" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:7" s="16" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
       <c r="D63" s="5"/>
@@ -2249,19 +2297,19 @@
       <c r="F63" s="5"/>
       <c r="G63" s="6"/>
     </row>
-    <row r="64" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D64" s="5"/>
       <c r="E64" s="5"/>
       <c r="F64" s="5"/>
       <c r="G64" s="6"/>
     </row>
-    <row r="65" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D65" s="5"/>
       <c r="E65" s="5"/>
       <c r="F65" s="5"/>
       <c r="G65" s="6"/>
     </row>
-    <row r="66" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
       <c r="D66" s="5"/>
@@ -2269,7 +2317,7 @@
       <c r="F66" s="5"/>
       <c r="G66" s="6"/>
     </row>
-    <row r="67" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
       <c r="D67" s="11"/>
@@ -2277,7 +2325,7 @@
       <c r="F67" s="11"/>
       <c r="G67" s="12"/>
     </row>
-    <row r="68" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B68" s="3"/>
       <c r="C68" s="3"/>
       <c r="D68" s="11"/>
@@ -2285,49 +2333,49 @@
       <c r="F68" s="11"/>
       <c r="G68" s="12"/>
     </row>
-    <row r="69" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D69" s="5"/>
       <c r="E69" s="5"/>
       <c r="F69" s="5"/>
       <c r="G69" s="6"/>
     </row>
-    <row r="70" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D70" s="5"/>
       <c r="E70" s="5"/>
       <c r="F70" s="5"/>
       <c r="G70" s="6"/>
     </row>
-    <row r="71" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D71" s="11"/>
       <c r="E71" s="11"/>
       <c r="F71" s="11"/>
       <c r="G71" s="12"/>
     </row>
-    <row r="72" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D72" s="5"/>
       <c r="E72" s="5"/>
       <c r="F72" s="5"/>
       <c r="G72" s="6"/>
     </row>
-    <row r="73" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D73" s="5"/>
       <c r="E73" s="5"/>
       <c r="F73" s="5"/>
       <c r="G73" s="6"/>
     </row>
-    <row r="74" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D74" s="5"/>
       <c r="E74" s="5"/>
       <c r="F74" s="5"/>
       <c r="G74" s="6"/>
     </row>
-    <row r="75" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D75" s="5"/>
       <c r="E75" s="5"/>
       <c r="F75" s="5"/>
       <c r="G75" s="6"/>
     </row>
-    <row r="76" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
       <c r="D76" s="5"/>
@@ -2335,7 +2383,7 @@
       <c r="F76" s="5"/>
       <c r="G76" s="6"/>
     </row>
-    <row r="77" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
       <c r="D77" s="5"/>
@@ -2343,7 +2391,7 @@
       <c r="F77" s="5"/>
       <c r="G77" s="6"/>
     </row>
-    <row r="78" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
       <c r="D78" s="5"/>
@@ -2351,127 +2399,127 @@
       <c r="F78" s="5"/>
       <c r="G78" s="6"/>
     </row>
-    <row r="79" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D79" s="5"/>
       <c r="E79" s="5"/>
       <c r="F79" s="5"/>
       <c r="G79" s="6"/>
     </row>
-    <row r="80" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D80" s="5"/>
       <c r="E80" s="5"/>
       <c r="F80" s="5"/>
       <c r="G80" s="6"/>
     </row>
-    <row r="81" spans="4:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="4:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D81" s="5"/>
       <c r="E81" s="5"/>
       <c r="F81" s="5"/>
       <c r="G81" s="6"/>
     </row>
-    <row r="82" spans="4:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="4:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D82" s="5"/>
       <c r="E82" s="5"/>
       <c r="F82" s="5"/>
       <c r="G82" s="6"/>
     </row>
-    <row r="83" spans="4:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="4:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D83" s="5"/>
       <c r="E83" s="5"/>
       <c r="F83" s="5"/>
       <c r="G83" s="6"/>
     </row>
-    <row r="84" spans="4:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="4:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D84" s="5"/>
       <c r="E84" s="5"/>
       <c r="F84" s="5"/>
       <c r="G84" s="6"/>
     </row>
-    <row r="85" spans="4:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="4:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D85" s="5"/>
       <c r="E85" s="5"/>
       <c r="F85" s="5"/>
       <c r="G85" s="6"/>
     </row>
-    <row r="86" spans="4:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="4:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D86" s="5"/>
       <c r="E86" s="5"/>
       <c r="F86" s="5"/>
       <c r="G86" s="6"/>
     </row>
-    <row r="87" spans="4:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="4:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D87" s="5"/>
       <c r="E87" s="5"/>
       <c r="F87" s="5"/>
       <c r="G87" s="6"/>
     </row>
-    <row r="88" spans="4:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="4:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D88" s="5"/>
       <c r="E88" s="5"/>
       <c r="F88" s="5"/>
       <c r="G88" s="6"/>
     </row>
-    <row r="89" spans="4:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="4:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D89" s="5"/>
       <c r="E89" s="5"/>
       <c r="F89" s="5"/>
       <c r="G89" s="6"/>
     </row>
-    <row r="90" spans="4:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="4:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D90" s="5"/>
       <c r="E90" s="5"/>
       <c r="F90" s="5"/>
       <c r="G90" s="6"/>
     </row>
-    <row r="91" spans="4:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="4:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D91" s="5"/>
       <c r="E91" s="5"/>
       <c r="F91" s="5"/>
       <c r="G91" s="6"/>
     </row>
-    <row r="92" spans="4:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="4:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D92" s="5"/>
       <c r="E92" s="5"/>
       <c r="F92" s="5"/>
       <c r="G92" s="6"/>
     </row>
-    <row r="93" spans="4:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="4:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D93" s="5"/>
       <c r="E93" s="5"/>
       <c r="F93" s="5"/>
       <c r="G93" s="6"/>
     </row>
-    <row r="94" spans="4:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="4:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D94" s="5"/>
       <c r="E94" s="5"/>
       <c r="F94" s="5"/>
       <c r="G94" s="6"/>
     </row>
-    <row r="95" spans="4:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="4:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D95" s="5"/>
       <c r="E95" s="5"/>
       <c r="F95" s="5"/>
       <c r="G95" s="6"/>
     </row>
-    <row r="96" spans="4:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="4:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D96" s="5"/>
       <c r="E96" s="5"/>
       <c r="F96" s="5"/>
       <c r="G96" s="6"/>
     </row>
-    <row r="97" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D97" s="5"/>
       <c r="E97" s="5"/>
       <c r="F97" s="5"/>
       <c r="G97" s="6"/>
     </row>
-    <row r="98" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D98" s="5"/>
       <c r="E98" s="5"/>
       <c r="F98" s="5"/>
       <c r="G98" s="6"/>
     </row>
-    <row r="99" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
       <c r="D99" s="11"/>
@@ -2479,7 +2527,7 @@
       <c r="F99" s="11"/>
       <c r="G99" s="12"/>
     </row>
-    <row r="100" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
       <c r="D100" s="5"/>
@@ -2487,7 +2535,7 @@
       <c r="F100" s="5"/>
       <c r="G100" s="6"/>
     </row>
-    <row r="101" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
       <c r="D101" s="5"/>
@@ -2495,19 +2543,19 @@
       <c r="F101" s="5"/>
       <c r="G101" s="6"/>
     </row>
-    <row r="102" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D102" s="5"/>
       <c r="E102" s="5"/>
       <c r="F102" s="5"/>
       <c r="G102" s="6"/>
     </row>
-    <row r="103" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D103" s="5"/>
       <c r="E103" s="5"/>
       <c r="F103" s="5"/>
       <c r="G103" s="6"/>
     </row>
-    <row r="104" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B104" s="16"/>
       <c r="C104" s="16"/>
       <c r="D104" s="5"/>
@@ -2515,7 +2563,7 @@
       <c r="F104" s="5"/>
       <c r="G104" s="6"/>
     </row>
-    <row r="105" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D105" s="5"/>
       <c r="E105" s="5"/>
       <c r="F105" s="5"/>
@@ -2535,20 +2583,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4DEFA5D-C6DF-4BEE-A0BF-87172BA2BD41}">
   <dimension ref="B1:G96"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="6.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.5546875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="6.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="24" style="2" customWidth="1"/>
-    <col min="6" max="6" width="30.85546875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="8.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="2"/>
+    <col min="6" max="6" width="30.88671875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="8.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="22" t="s">
         <v>8</v>
       </c>
@@ -2568,7 +2616,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="2:7" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:7" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3">
         <v>1</v>
       </c>
@@ -2586,7 +2634,7 @@
       </c>
       <c r="G3" s="23"/>
     </row>
-    <row r="4" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4">
         <v>2</v>
       </c>
@@ -2604,7 +2652,7 @@
       </c>
       <c r="G4" s="23"/>
     </row>
-    <row r="5" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>3</v>
       </c>
@@ -2622,7 +2670,7 @@
       </c>
       <c r="G5" s="23"/>
     </row>
-    <row r="6" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>4</v>
       </c>
@@ -2640,7 +2688,7 @@
       </c>
       <c r="G6" s="23"/>
     </row>
-    <row r="7" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>5</v>
       </c>
@@ -2660,7 +2708,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8">
         <v>6</v>
       </c>
@@ -2680,7 +2728,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9">
         <v>7</v>
       </c>
@@ -2698,7 +2746,7 @@
       </c>
       <c r="G9" s="23"/>
     </row>
-    <row r="10" spans="2:7" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:7" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10">
         <v>8</v>
       </c>
@@ -2716,7 +2764,7 @@
       </c>
       <c r="G10" s="23"/>
     </row>
-    <row r="11" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11">
         <v>9</v>
       </c>
@@ -2734,7 +2782,7 @@
       </c>
       <c r="G11" s="25"/>
     </row>
-    <row r="12" spans="2:7" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:7" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12">
         <v>10</v>
       </c>
@@ -2752,7 +2800,7 @@
       </c>
       <c r="G12" s="25"/>
     </row>
-    <row r="13" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="7"/>
@@ -2760,13 +2808,13 @@
       <c r="F13" s="7"/>
       <c r="G13" s="8"/>
     </row>
-    <row r="14" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
       <c r="G14" s="6"/>
     </row>
-    <row r="15" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="5"/>
@@ -2774,7 +2822,7 @@
       <c r="F15" s="5"/>
       <c r="G15" s="6"/>
     </row>
-    <row r="16" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
       <c r="D16" s="5"/>
@@ -2782,13 +2830,13 @@
       <c r="F16" s="5"/>
       <c r="G16" s="6"/>
     </row>
-    <row r="17" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
       <c r="G17" s="6"/>
     </row>
-    <row r="18" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="5"/>
@@ -2796,31 +2844,31 @@
       <c r="F18" s="5"/>
       <c r="G18" s="6"/>
     </row>
-    <row r="19" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D19" s="5"/>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
       <c r="G19" s="6"/>
     </row>
-    <row r="20" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
       <c r="G20" s="8"/>
     </row>
-    <row r="21" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
       <c r="F21" s="7"/>
       <c r="G21" s="8"/>
     </row>
-    <row r="22" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
       <c r="G22" s="6"/>
     </row>
-    <row r="23" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
       <c r="D23" s="5"/>
@@ -2828,7 +2876,7 @@
       <c r="F23" s="5"/>
       <c r="G23" s="6"/>
     </row>
-    <row r="24" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
       <c r="D24" s="5"/>
@@ -2836,7 +2884,7 @@
       <c r="F24" s="5"/>
       <c r="G24" s="6"/>
     </row>
-    <row r="25" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
       <c r="D25" s="5"/>
@@ -2844,7 +2892,7 @@
       <c r="F25" s="5"/>
       <c r="G25" s="6"/>
     </row>
-    <row r="26" spans="2:7" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:7" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
       <c r="D26" s="5"/>
@@ -2852,37 +2900,37 @@
       <c r="F26" s="5"/>
       <c r="G26" s="6"/>
     </row>
-    <row r="27" spans="2:7" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:7" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="10"/>
       <c r="G27" s="9"/>
     </row>
-    <row r="28" spans="2:7" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:7" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="10"/>
       <c r="G28" s="9"/>
     </row>
-    <row r="29" spans="2:7" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:7" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
       <c r="F29" s="10"/>
       <c r="G29" s="9"/>
     </row>
-    <row r="30" spans="2:7" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:7" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
       <c r="F30" s="10"/>
       <c r="G30" s="9"/>
     </row>
-    <row r="31" spans="2:7" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:7" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
       <c r="F31" s="10"/>
       <c r="G31" s="9"/>
     </row>
-    <row r="32" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
       <c r="D32" s="9"/>
@@ -2890,13 +2938,13 @@
       <c r="F32" s="10"/>
       <c r="G32" s="9"/>
     </row>
-    <row r="33" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D33" s="11"/>
       <c r="E33" s="11"/>
       <c r="F33" s="11"/>
       <c r="G33" s="12"/>
     </row>
-    <row r="34" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
       <c r="D34" s="5"/>
@@ -2904,7 +2952,7 @@
       <c r="F34" s="5"/>
       <c r="G34" s="6"/>
     </row>
-    <row r="35" spans="2:7" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:7" s="13" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
       <c r="D35" s="5"/>
@@ -2912,7 +2960,7 @@
       <c r="F35" s="5"/>
       <c r="G35" s="6"/>
     </row>
-    <row r="36" spans="2:7" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:7" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="13"/>
       <c r="C36" s="13"/>
       <c r="D36" s="11"/>
@@ -2920,25 +2968,25 @@
       <c r="F36" s="11"/>
       <c r="G36" s="12"/>
     </row>
-    <row r="37" spans="2:7" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:7" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D37" s="11"/>
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
       <c r="G37" s="12"/>
     </row>
-    <row r="38" spans="2:7" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:7" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D38" s="11"/>
       <c r="E38" s="11"/>
       <c r="F38" s="11"/>
       <c r="G38" s="12"/>
     </row>
-    <row r="39" spans="2:7" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:7" s="4" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D39" s="11"/>
       <c r="E39" s="11"/>
       <c r="F39" s="11"/>
       <c r="G39" s="12"/>
     </row>
-    <row r="40" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
       <c r="D40" s="14"/>
@@ -2946,25 +2994,25 @@
       <c r="F40" s="14"/>
       <c r="G40" s="15"/>
     </row>
-    <row r="41" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D41" s="5"/>
       <c r="E41" s="5"/>
       <c r="F41" s="5"/>
       <c r="G41" s="6"/>
     </row>
-    <row r="42" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D42" s="5"/>
       <c r="E42" s="5"/>
       <c r="F42" s="5"/>
       <c r="G42" s="6"/>
     </row>
-    <row r="43" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D43" s="5"/>
       <c r="E43" s="5"/>
       <c r="F43" s="5"/>
       <c r="G43" s="6"/>
     </row>
-    <row r="44" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
       <c r="D44" s="5"/>
@@ -2972,19 +3020,19 @@
       <c r="F44" s="5"/>
       <c r="G44" s="6"/>
     </row>
-    <row r="45" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D45" s="5"/>
       <c r="E45" s="5"/>
       <c r="F45" s="5"/>
       <c r="G45" s="6"/>
     </row>
-    <row r="46" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D46" s="11"/>
       <c r="E46" s="11"/>
       <c r="F46" s="11"/>
       <c r="G46" s="12"/>
     </row>
-    <row r="47" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
       <c r="D47" s="11"/>
@@ -2992,43 +3040,43 @@
       <c r="F47" s="11"/>
       <c r="G47" s="12"/>
     </row>
-    <row r="48" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D48" s="5"/>
       <c r="E48" s="5"/>
       <c r="F48" s="5"/>
       <c r="G48" s="6"/>
     </row>
-    <row r="49" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D49" s="5"/>
       <c r="E49" s="5"/>
       <c r="F49" s="5"/>
       <c r="G49" s="6"/>
     </row>
-    <row r="50" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D50" s="11"/>
       <c r="E50" s="11"/>
       <c r="F50" s="11"/>
       <c r="G50" s="12"/>
     </row>
-    <row r="51" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D51" s="5"/>
       <c r="E51" s="5"/>
       <c r="F51" s="5"/>
       <c r="G51" s="6"/>
     </row>
-    <row r="52" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D52" s="5"/>
       <c r="E52" s="5"/>
       <c r="F52" s="5"/>
       <c r="G52" s="6"/>
     </row>
-    <row r="53" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D53" s="5"/>
       <c r="E53" s="5"/>
       <c r="F53" s="5"/>
       <c r="G53" s="6"/>
     </row>
-    <row r="54" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
       <c r="D54" s="5"/>
@@ -3036,19 +3084,19 @@
       <c r="F54" s="5"/>
       <c r="G54" s="6"/>
     </row>
-    <row r="55" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D55" s="5"/>
       <c r="E55" s="5"/>
       <c r="F55" s="5"/>
       <c r="G55" s="6"/>
     </row>
-    <row r="56" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D56" s="5"/>
       <c r="E56" s="5"/>
       <c r="F56" s="5"/>
       <c r="G56" s="6"/>
     </row>
-    <row r="57" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
       <c r="D57" s="5"/>
@@ -3056,121 +3104,121 @@
       <c r="F57" s="5"/>
       <c r="G57" s="6"/>
     </row>
-    <row r="58" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D58" s="5"/>
       <c r="E58" s="5"/>
       <c r="F58" s="5"/>
       <c r="G58" s="6"/>
     </row>
-    <row r="59" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D59" s="5"/>
       <c r="E59" s="5"/>
       <c r="F59" s="5"/>
       <c r="G59" s="6"/>
     </row>
-    <row r="60" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D60" s="5"/>
       <c r="E60" s="5"/>
       <c r="F60" s="5"/>
       <c r="G60" s="6"/>
     </row>
-    <row r="61" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D61" s="5"/>
       <c r="E61" s="5"/>
       <c r="F61" s="5"/>
       <c r="G61" s="6"/>
     </row>
-    <row r="62" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D62" s="5"/>
       <c r="E62" s="5"/>
       <c r="F62" s="5"/>
       <c r="G62" s="6"/>
     </row>
-    <row r="63" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D63" s="5"/>
       <c r="E63" s="5"/>
       <c r="F63" s="5"/>
       <c r="G63" s="6"/>
     </row>
-    <row r="64" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D64" s="5"/>
       <c r="E64" s="5"/>
       <c r="F64" s="5"/>
       <c r="G64" s="6"/>
     </row>
-    <row r="65" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D65" s="5"/>
       <c r="E65" s="5"/>
       <c r="F65" s="5"/>
       <c r="G65" s="6"/>
     </row>
-    <row r="66" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D66" s="5"/>
       <c r="E66" s="5"/>
       <c r="F66" s="5"/>
       <c r="G66" s="6"/>
     </row>
-    <row r="67" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D67" s="5"/>
       <c r="E67" s="5"/>
       <c r="F67" s="5"/>
       <c r="G67" s="6"/>
     </row>
-    <row r="68" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D68" s="5"/>
       <c r="E68" s="5"/>
       <c r="F68" s="5"/>
       <c r="G68" s="6"/>
     </row>
-    <row r="69" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D69" s="5"/>
       <c r="E69" s="5"/>
       <c r="F69" s="5"/>
       <c r="G69" s="6"/>
     </row>
-    <row r="70" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D70" s="5"/>
       <c r="E70" s="5"/>
       <c r="F70" s="5"/>
       <c r="G70" s="6"/>
     </row>
-    <row r="71" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D71" s="5"/>
       <c r="E71" s="5"/>
       <c r="F71" s="5"/>
       <c r="G71" s="6"/>
     </row>
-    <row r="72" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D72" s="5"/>
       <c r="E72" s="5"/>
       <c r="F72" s="5"/>
       <c r="G72" s="6"/>
     </row>
-    <row r="73" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D73" s="5"/>
       <c r="E73" s="5"/>
       <c r="F73" s="5"/>
       <c r="G73" s="6"/>
     </row>
-    <row r="74" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D74" s="5"/>
       <c r="E74" s="5"/>
       <c r="F74" s="5"/>
       <c r="G74" s="6"/>
     </row>
-    <row r="75" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D75" s="5"/>
       <c r="E75" s="5"/>
       <c r="F75" s="5"/>
       <c r="G75" s="6"/>
     </row>
-    <row r="76" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D76" s="5"/>
       <c r="E76" s="5"/>
       <c r="F76" s="5"/>
       <c r="G76" s="6"/>
     </row>
-    <row r="77" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
       <c r="D77" s="5"/>
@@ -3178,19 +3226,19 @@
       <c r="F77" s="5"/>
       <c r="G77" s="6"/>
     </row>
-    <row r="78" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D78" s="11"/>
       <c r="E78" s="11"/>
       <c r="F78" s="11"/>
       <c r="G78" s="12"/>
     </row>
-    <row r="79" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D79" s="5"/>
       <c r="E79" s="5"/>
       <c r="F79" s="5"/>
       <c r="G79" s="6"/>
     </row>
-    <row r="80" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
       <c r="D80" s="5"/>
@@ -3198,13 +3246,13 @@
       <c r="F80" s="5"/>
       <c r="G80" s="6"/>
     </row>
-    <row r="81" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D81" s="5"/>
       <c r="E81" s="5"/>
       <c r="F81" s="5"/>
       <c r="G81" s="6"/>
     </row>
-    <row r="82" spans="2:7" s="16" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:7" s="16" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
       <c r="D82" s="5"/>
@@ -3212,7 +3260,7 @@
       <c r="F82" s="5"/>
       <c r="G82" s="6"/>
     </row>
-    <row r="83" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B83" s="16"/>
       <c r="C83" s="16"/>
       <c r="D83" s="5"/>
@@ -3220,20 +3268,20 @@
       <c r="F83" s="5"/>
       <c r="G83" s="6"/>
     </row>
-    <row r="84" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D84" s="5"/>
       <c r="E84" s="5"/>
       <c r="F84" s="5"/>
       <c r="G84" s="6"/>
     </row>
-    <row r="85" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="86" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="87" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="88" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="89" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="90" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="91" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="96" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <conditionalFormatting sqref="D3:D12">
     <cfRule type="duplicateValues" dxfId="4" priority="3"/>

--- a/IA_CCBS_BANK_SIDE/AccountOther/LoanAccountOpening_InstantProcess.xlsx
+++ b/IA_CCBS_BANK_SIDE/AccountOther/LoanAccountOpening_InstantProcess.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kmilos\source\repos\iApply_CCBS_API\IA_CCBS_BANK_SIDE\AccountOther\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4234C863-96FE-4972-B220-969F8E23A493}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D155E4EF-17CF-43A2-A095-CAF2649A74DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{68F28061-2ECD-4B0A-AB1D-3A449686159F}"/>
   </bookViews>
@@ -535,7 +535,7 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -614,7 +614,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="20% - Accent4" xfId="1" builtinId="42"/>
@@ -1660,7 +1659,7 @@
         <v>24</v>
       </c>
       <c r="E11" s="26" t="s">
-        <v>4</v>
+        <v>111</v>
       </c>
       <c r="F11" s="26" t="s">
         <v>32</v>
@@ -2031,10 +2030,10 @@
       <c r="B32">
         <v>30</v>
       </c>
-      <c r="C32" s="28" t="s">
+      <c r="C32" s="26" t="s">
         <v>107</v>
       </c>
-      <c r="D32" s="28" t="s">
+      <c r="D32" s="26" t="s">
         <v>107</v>
       </c>
       <c r="E32" s="26" t="s">
@@ -2043,16 +2042,16 @@
       <c r="F32" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="G32" s="28"/>
+      <c r="G32" s="26"/>
     </row>
     <row r="33" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33">
         <v>31</v>
       </c>
-      <c r="C33" s="28" t="s">
+      <c r="C33" s="26" t="s">
         <v>108</v>
       </c>
-      <c r="D33" s="28" t="s">
+      <c r="D33" s="26" t="s">
         <v>108</v>
       </c>
       <c r="E33" s="26" t="s">
@@ -2061,25 +2060,25 @@
       <c r="F33" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="G33" s="28"/>
+      <c r="G33" s="26"/>
     </row>
     <row r="34" spans="2:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34">
         <v>32</v>
       </c>
-      <c r="C34" s="28" t="s">
+      <c r="C34" s="26" t="s">
         <v>109</v>
       </c>
-      <c r="D34" s="28" t="s">
+      <c r="D34" s="26" t="s">
         <v>109</v>
       </c>
-      <c r="E34" s="28" t="s">
+      <c r="E34" s="26" t="s">
         <v>111</v>
       </c>
       <c r="F34" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="G34" s="28"/>
+      <c r="G34" s="26"/>
     </row>
     <row r="35" spans="2:7" s="3" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="2"/>

--- a/IA_CCBS_BANK_SIDE/AccountOther/LoanAccountOpening_InstantProcess.xlsx
+++ b/IA_CCBS_BANK_SIDE/AccountOther/LoanAccountOpening_InstantProcess.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kmilos\source\repos\iApply_CCBS_API\IA_CCBS_BANK_SIDE\AccountOther\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D155E4EF-17CF-43A2-A095-CAF2649A74DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DD8362C-B59F-443D-A3BD-791538BF55DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{68F28061-2ECD-4B0A-AB1D-3A449686159F}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="113">
   <si>
     <t>Description</t>
   </si>
@@ -367,6 +367,9 @@
   </si>
   <si>
     <t>string</t>
+  </si>
+  <si>
+    <t>varchar (20)</t>
   </si>
 </sst>
 </file>
@@ -1983,7 +1986,7 @@
         <v>78</v>
       </c>
       <c r="E29" s="26" t="s">
-        <v>4</v>
+        <v>112</v>
       </c>
       <c r="F29" s="26" t="s">
         <v>32</v>
@@ -2001,7 +2004,7 @@
         <v>80</v>
       </c>
       <c r="E30" s="26" t="s">
-        <v>4</v>
+        <v>112</v>
       </c>
       <c r="F30" s="26" t="s">
         <v>32</v>
